--- a/docs/oc-regiones/suministro-de-combustibles/arica-y-parinacota.xlsx
+++ b/docs/oc-regiones/suministro-de-combustibles/arica-y-parinacota.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>2244.32</v>
+        <v>2225.31</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>5290.17</v>
+        <v>5262.99</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>3740.53</v>
+        <v>3735.76</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>2244.32</v>
+        <v>2241.46</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>4274.89</v>
+        <v>4288.95</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>8015.41</v>
+        <v>8153.77</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>2671.8</v>
+        <v>2684.25</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>21374.43</v>
+        <v>21336.52</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>21374.43</v>
+        <v>21286.33</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>15431.44</v>
+        <v>15407.52</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>11755.94</v>
+        <v>11816.65</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>4061.14</v>
+        <v>4089.8</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>44886.3</v>
+        <v>45203.09</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>2671.8</v>
+        <v>2690.66</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>27375.04</v>
+        <v>27027.32</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>3929.43</v>
+        <v>3890.34</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>2401.32</v>
+        <v>2377.43</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>2401.32</v>
+        <v>2392.71</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>8732.07</v>
+        <v>8713.17</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>5506.66</v>
+        <v>5527.8</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>2292.17</v>
+        <v>2302.56</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>3274.53</v>
+        <v>3269.93</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>7640.56</v>
+        <v>7693.15</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>2277.98</v>
+        <v>2297.45</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>4911.79</v>
+        <v>4953.76</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>3366.21</v>
+        <v>3394.98</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>65490.53</v>
+        <v>66050.2</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>11002.71</v>
+        <v>11137.93</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>3274.53</v>
+        <v>3316.6</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>2292.17</v>
+        <v>2321.62</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>3274.53</v>
+        <v>3292.43</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>4597.46</v>
+        <v>4531.57</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>5656.33</v>
+        <v>5636.92</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>2828.16</v>
+        <v>2810.44</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>4525.06</v>
+        <v>4586</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>5975.34</v>
+        <v>6066.31</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>16968.98</v>
+        <v>17483.54</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>4506.96</v>
+        <v>4640.92</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>9050.120000000001</v>
+        <v>9319.120000000001</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>29117.65</v>
+        <v>29268.07</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>34384.35</v>
+        <v>34561.97</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>4561.38</v>
+        <v>4602.01</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>5799.23</v>
+        <v>5793.25</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>2784.08</v>
+        <v>2781.21</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>3016.17</v>
+        <v>3013.06</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>80352.37</v>
+        <v>80234.16</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>2552.14</v>
+        <v>2538.25</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>5800.33</v>
+        <v>5768.74</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>4640.26</v>
+        <v>4622.35</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>6059.6</v>
+        <v>6036.22</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>2424.54</v>
+        <v>2437.09</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>23201.32</v>
+        <v>23223.68</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>16485.45</v>
+        <v>17213.48</v>
       </c>
     </row>
     <row r="55">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>7651.45</v>
+        <v>7873.7</v>
       </c>
     </row>
     <row r="56">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>16485.45</v>
+        <v>16757.16</v>
       </c>
     </row>
     <row r="57">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>2417.87</v>
+        <v>2457.72</v>
       </c>
     </row>
     <row r="58">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>4409.31</v>
+        <v>4420.16</v>
       </c>
     </row>
     <row r="59">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>5357.31</v>
+        <v>5288.34</v>
       </c>
     </row>
     <row r="60">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>9891.27</v>
+        <v>9763.93</v>
       </c>
     </row>
     <row r="61">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>5522.63</v>
+        <v>5497.93</v>
       </c>
     </row>
     <row r="62">
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>3297.09</v>
+        <v>3299.93</v>
       </c>
     </row>
     <row r="63">
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>21980.6</v>
+        <v>21726.85</v>
       </c>
     </row>
     <row r="64">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>3313.58</v>
+        <v>3264.15</v>
       </c>
     </row>
     <row r="65">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>5495.15</v>
+        <v>5459.95</v>
       </c>
     </row>
     <row r="66">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>4396.12</v>
+        <v>4301.54</v>
       </c>
     </row>
     <row r="67">
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>8727.950000000001</v>
+        <v>8540.17</v>
       </c>
     </row>
     <row r="68">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>74960.92999999999</v>
+        <v>73348.14999999999</v>
       </c>
     </row>
     <row r="69">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>18798.91</v>
+        <v>18394.45</v>
       </c>
     </row>
     <row r="70">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>85951.87</v>
+        <v>83211.14</v>
       </c>
     </row>
     <row r="71">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>80533.59</v>
+        <v>77965.63</v>
       </c>
     </row>
     <row r="72">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>2339.94</v>
+        <v>2293.79</v>
       </c>
     </row>
     <row r="73">
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>33411.81</v>
+        <v>32805.89</v>
       </c>
     </row>
     <row r="74">
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>3091.71</v>
+        <v>3117.95</v>
       </c>
     </row>
     <row r="75">
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>5305.79</v>
+        <v>5350.82</v>
       </c>
     </row>
     <row r="76">
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>6682.36</v>
+        <v>6671.19</v>
       </c>
     </row>
     <row r="77">
@@ -5144,7 +5144,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>3341.18</v>
+        <v>3382.3</v>
       </c>
     </row>
     <row r="78">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>10023.54</v>
+        <v>10156.98</v>
       </c>
     </row>
     <row r="79">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>9026.76</v>
+        <v>9146.93</v>
       </c>
     </row>
     <row r="80">
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>31614.25</v>
+        <v>32392.28</v>
       </c>
     </row>
     <row r="81">
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>22274.54</v>
+        <v>22695.81</v>
       </c>
     </row>
     <row r="82">
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>2895.69</v>
+        <v>2921.78</v>
       </c>
     </row>
     <row r="83">
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>9287.370000000001</v>
+        <v>9316.59</v>
       </c>
     </row>
     <row r="84">
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>4009.42</v>
+        <v>4026.04</v>
       </c>
     </row>
     <row r="85">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>11025.9</v>
+        <v>11048.74</v>
       </c>
     </row>
     <row r="86">
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>2338.83</v>
+        <v>2343.67</v>
       </c>
     </row>
     <row r="87">
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>6682.36</v>
+        <v>6653.66</v>
       </c>
     </row>
     <row r="88">
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>22280.7</v>
+        <v>22400.68</v>
       </c>
     </row>
     <row r="89">
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>2663.89</v>
+        <v>2693.68</v>
       </c>
     </row>
     <row r="90">
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>77627.35000000001</v>
+        <v>77431.35000000001</v>
       </c>
     </row>
     <row r="91">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>3019.03</v>
+        <v>3011.41</v>
       </c>
     </row>
     <row r="92">
@@ -6059,7 +6059,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>18938.59</v>
+        <v>19079.69</v>
       </c>
     </row>
     <row r="93">
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>5263.82</v>
+        <v>5303.03</v>
       </c>
     </row>
     <row r="94">
@@ -6181,7 +6181,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>2785.09</v>
+        <v>2754.79</v>
       </c>
     </row>
     <row r="95">
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>8912.280000000001</v>
+        <v>8941.84</v>
       </c>
     </row>
     <row r="96">
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>8766.34</v>
+        <v>8794.24</v>
       </c>
     </row>
     <row r="97">
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>2767.37</v>
+        <v>2799.83</v>
       </c>
     </row>
     <row r="98">
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>61916.45</v>
+        <v>62497.17</v>
       </c>
     </row>
     <row r="99">
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>6032.87</v>
+        <v>6089.45</v>
       </c>
     </row>
     <row r="100">
@@ -6547,7 +6547,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>6716.96</v>
+        <v>6779.96</v>
       </c>
     </row>
     <row r="101">
@@ -6608,7 +6608,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>4427.79</v>
+        <v>4352.98</v>
       </c>
     </row>
     <row r="102">
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>2379.94</v>
+        <v>2347.24</v>
       </c>
     </row>
     <row r="103">
@@ -6730,7 +6730,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>2775.64</v>
+        <v>2816.97</v>
       </c>
     </row>
     <row r="104">
@@ -6791,7 +6791,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>2767.37</v>
+        <v>2808.58</v>
       </c>
     </row>
     <row r="105">
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>2767.37</v>
+        <v>2808.58</v>
       </c>
     </row>
     <row r="106">
@@ -6913,7 +6913,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>2379.94</v>
+        <v>2425.19</v>
       </c>
     </row>
     <row r="107">
@@ -6974,7 +6974,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>7159.99</v>
+        <v>7321.46</v>
       </c>
     </row>
     <row r="108">
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>22138.97</v>
+        <v>22638.26</v>
       </c>
     </row>
     <row r="109">
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>2379.94</v>
+        <v>2433.61</v>
       </c>
     </row>
     <row r="110">
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>2379.94</v>
+        <v>2387.3</v>
       </c>
     </row>
     <row r="111">
@@ -7218,7 +7218,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>3320.85</v>
+        <v>3312.06</v>
       </c>
     </row>
     <row r="112">
@@ -7279,7 +7279,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>4652.51</v>
+        <v>4590.53</v>
       </c>
     </row>
     <row r="113">
@@ -7405,7 +7405,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>5120.32</v>
+        <v>5044.46</v>
       </c>
     </row>
     <row r="115">
@@ -7466,7 +7466,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>6758.18</v>
+        <v>6658.05</v>
       </c>
     </row>
     <row r="116">
@@ -7527,7 +7527,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>5267.09</v>
+        <v>5287.65</v>
       </c>
     </row>
     <row r="117">
@@ -7588,7 +7588,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>7519.04</v>
+        <v>7594.66</v>
       </c>
     </row>
     <row r="118">
@@ -7649,7 +7649,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>7666.06</v>
+        <v>7742.83</v>
       </c>
     </row>
     <row r="119">
@@ -7710,7 +7710,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>34365.23</v>
+        <v>34438.48</v>
       </c>
     </row>
     <row r="120">
@@ -7771,7 +7771,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>25303.41</v>
+        <v>25361.43</v>
       </c>
     </row>
     <row r="121">
@@ -7832,7 +7832,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>35555.32</v>
+        <v>35793.31</v>
       </c>
     </row>
     <row r="122">
@@ -7893,7 +7893,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>2685.37</v>
+        <v>2703.35</v>
       </c>
     </row>
     <row r="123">
@@ -7954,7 +7954,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>4684.36</v>
+        <v>4715.72</v>
       </c>
     </row>
     <row r="124">
@@ -8015,7 +8015,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>4833.67</v>
+        <v>4756.17</v>
       </c>
     </row>
     <row r="125">
@@ -8076,7 +8076,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>21482.97</v>
+        <v>21233</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/suministro-de-combustibles/arica-y-parinacota.xlsx
+++ b/docs/oc-regiones/suministro-de-combustibles/arica-y-parinacota.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M125"/>
+  <dimension ref="A1:M134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>720-519-CM25</t>
+          <t>941739-11-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,27 +524,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-02-07</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>70.770.800-K</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>2225.31</v>
+        <v>20669.91</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>720-506-CM25</t>
+          <t>4022-120-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,27 +585,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>69.250.800-9</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PUTRE</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>5262.99</v>
+        <v>21254.21</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5611-131-CM25</t>
+          <t>830715-33-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,27 +646,27 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>61.813.000-2</t>
+          <t>60.511.139-4</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>SERVICIO REGIONAL DE LA VIVIENDA Y URBAN</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE PARINACOTA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>3735.76</v>
+        <v>5766.45</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1087-327-CM25</t>
+          <t>1110404-978-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,27 +707,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>2241.46</v>
+        <v>2435.66</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>707409-149-CM25</t>
+          <t>1110404-1042-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>4288.95</v>
+        <v>70119.72</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>4017-107-CM25</t>
+          <t>963423-2640-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,27 +829,27 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>69.250.800-9</t>
+          <t>61.980.850-9</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Putre</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>8153.77</v>
+        <v>2168.64</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>5702-888-CM25</t>
+          <t>707409-98-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,27 +890,27 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>2684.25</v>
+        <v>4139.29</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>978-272-CM25</t>
+          <t>5702-716-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -951,12 +951,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -966,12 +966,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>21336.52</v>
+        <v>3139.82</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>4022-804-CM25</t>
+          <t>5702-715-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1012,27 +1012,27 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>69.250.800-9</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Putre</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>21286.33</v>
+        <v>3139.82</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>720-1088-CM25</t>
+          <t>720-519-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>15407.52</v>
+        <v>2225.31</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>720-479-CM25</t>
+          <t>720-506-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>11816.65</v>
+        <v>5262.99</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1774-236-CM25</t>
+          <t>5611-131-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1210,12 +1210,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>60.804.001-3</t>
+          <t>61.813.000-2</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>ADMINISTRACIÓN ADUANA DE ARICA</t>
+          <t>SERVICIO REGIONAL DE LA VIVIENDA Y URBAN</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>4089.8</v>
+        <v>3735.76</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>720-1096-CM25</t>
+          <t>1087-327-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>45203.09</v>
+        <v>2241.46</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>5702-916-CM25</t>
+          <t>707409-149-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>2690.66</v>
+        <v>4288.95</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3527-339-CM25</t>
+          <t>4017-107-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1378,27 +1378,27 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>61.101.037-0</t>
+          <t>69.250.800-9</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>Ilustre Municipalidad de Putre</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>27027.32</v>
+        <v>8153.77</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>548849-100-CM25</t>
+          <t>5702-888-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1439,12 +1439,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>61.979.440-0</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Instituto de Prevision Social</t>
+          <t>Direc.Reg.Arica y Parinacota</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>3890.34</v>
+        <v>2684.25</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3527-344-CM25</t>
+          <t>978-272-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1515,12 +1515,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>61.101.037-0</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>2377.43</v>
+        <v>21336.52</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>5648-75-CM25</t>
+          <t>4022-804-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1561,27 +1561,27 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>61.979.070-7</t>
+          <t>69.250.800-9</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ministerio de Vivienda y Urbanismo</t>
+          <t>Ilustre Municipalidad de Putre</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>2392.71</v>
+        <v>21286.33</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>720-1126-CM25</t>
+          <t>720-1088-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1622,12 +1622,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>8713.17</v>
+        <v>15407.52</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1075963-60313-CM25</t>
+          <t>720-479-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1698,12 +1698,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>5527.8</v>
+        <v>11816.65</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>838099-109-CM25</t>
+          <t>1774-236-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1759,12 +1759,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>73.923.800-5</t>
+          <t>60.804.001-3</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Zona Bienestar "Arica" Bienestar Social</t>
+          <t>ADMINISTRACIÓN ADUANA DE ARICA</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>2302.56</v>
+        <v>4089.8</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1606-586-CM25</t>
+          <t>720-1096-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1820,12 +1820,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>60.108.000-1</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>AGENCIA CHILENA DE COOPERACION INTERNACIONAL PARA EL DESARROLLO</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>3269.93</v>
+        <v>45203.09</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1087-386-CM25</t>
+          <t>5702-916-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1866,12 +1866,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>Direc.Reg.Arica y Parinacota</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>7693.15</v>
+        <v>2690.66</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>5667-318-CM25</t>
+          <t>3527-339-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>61.979.080-4</t>
+          <t>61.101.037-0</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>SEREMI de Educación Arica y Parinacota</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>2297.45</v>
+        <v>27027.32</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>5702-964-CM25</t>
+          <t>548849-100-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1993,7 +1993,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2003,12 +2003,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>61.979.440-0</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>Instituto de Prevision Social</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2033,13 +2033,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>4953.76</v>
+        <v>3890.34</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1075963-61121-CM25</t>
+          <t>3527-344-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2054,22 +2054,22 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>61.101.037-0</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2094,13 +2094,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>3394.98</v>
+        <v>2377.43</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>978-299-CM25</t>
+          <t>5648-75-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.979.070-7</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>Ministerio de Vivienda y Urbanismo</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2155,13 +2155,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>66050.2</v>
+        <v>2392.71</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>720-1182-CM25</t>
+          <t>720-1126-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2216,13 +2216,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>11137.93</v>
+        <v>8713.17</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>5702-978-CM25</t>
+          <t>1075963-60313-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2237,7 +2237,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2277,13 +2277,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>3316.6</v>
+        <v>5527.8</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1110404-1633-CM25</t>
+          <t>838099-109-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2308,12 +2308,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>73.923.800-5</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>Zona Bienestar "Arica" Bienestar Social</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2338,13 +2338,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>2321.62</v>
+        <v>2302.56</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>978-301-CM25</t>
+          <t>1606-586-CM25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2359,7 +2359,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2369,12 +2369,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>60.108.000-1</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>AGENCIA CHILENA DE COOPERACION INTERNACIONAL PARA EL DESARROLLO</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2399,13 +2399,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>3292.43</v>
+        <v>3269.93</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1075963-90-CM26</t>
+          <t>1087-386-CM25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2415,27 +2415,27 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2460,13 +2460,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>4531.57</v>
+        <v>7693.15</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2021-3-CM26</t>
+          <t>978-299-CM25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2476,12 +2476,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2491,12 +2491,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>61.101.040-0</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Estado Mayor Conjunto</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2521,13 +2521,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>5636.92</v>
+        <v>66050.2</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1232837-29-CM26</t>
+          <t>1075963-61121-CM25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2537,27 +2537,27 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>65.166.511-6</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE FOMENTO   PRODUCTIVO DE ARICA</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2582,13 +2582,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>2810.44</v>
+        <v>3394.98</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1489-2-CM26</t>
+          <t>5702-964-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2613,12 +2613,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>61.979.110-k</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>SERPLAC ARICA Y PARINACOTA</t>
+          <t>Direc.Reg.Arica y Parinacota</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2643,13 +2643,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>4586</v>
+        <v>4953.76</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>830715-2-CM26</t>
+          <t>5667-318-CM25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2659,27 +2659,27 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>60.511.139-4</t>
+          <t>61.979.080-4</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE PARINACOTA</t>
+          <t>SEREMI de Educación Arica y Parinacota</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2704,13 +2704,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>6066.31</v>
+        <v>2297.45</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>941739-7-CM26</t>
+          <t>720-1182-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2720,27 +2720,27 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2025-12-27</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>70.770.800-K</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2765,13 +2765,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>17483.54</v>
+        <v>11137.93</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1075963-1737-CM26</t>
+          <t>5702-978-CM25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2781,27 +2781,27 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>Direc.Reg.Arica y Parinacota</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2826,13 +2826,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>4640.92</v>
+        <v>3316.6</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>5358-18-CM26</t>
+          <t>1110404-1633-CM25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2842,27 +2842,27 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2887,28 +2887,28 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>9319.120000000001</v>
+        <v>2321.62</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2366-56-CM26</t>
+          <t>978-301-CM25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2239-13-LR25</t>
+          <t>2239-3-LR24</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2948,43 +2948,43 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>29268.07</v>
+        <v>3292.43</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2366-57-CM26</t>
+          <t>1075963-90-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2239-13-LR25</t>
+          <t>2239-3-LR24</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3009,43 +3009,43 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>34561.97</v>
+        <v>4531.57</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1075963-2331-CM26</t>
+          <t>2021-3-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2239-13-LR25</t>
+          <t>2239-3-LR24</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>61.101.040-0</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>Estado Mayor Conjunto</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3070,28 +3070,28 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>4602.01</v>
+        <v>5636.92</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>720-10-CM26</t>
+          <t>1232837-29-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2239-13-LR25</t>
+          <t>2239-3-LR24</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3101,12 +3101,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>65.166.511-6</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>CORPORACION MUNICIPAL DE FOMENTO   PRODUCTIVO DE ARICA</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3131,28 +3131,28 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>5793.25</v>
+        <v>2810.44</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>720-11-CM26</t>
+          <t>1489-2-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2239-13-LR25</t>
+          <t>2239-3-LR24</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3162,12 +3162,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.979.110-k</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>SERPLAC ARICA Y PARINACOTA</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3192,43 +3192,43 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>2781.21</v>
+        <v>4586</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>720-12-CM26</t>
+          <t>830715-2-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2239-13-LR25</t>
+          <t>2239-3-LR24</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>60.511.139-4</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE PARINACOTA</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3253,43 +3253,43 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>3013.06</v>
+        <v>6066.31</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>720-9-CM26</t>
+          <t>941739-7-CM26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2239-13-LR25</t>
+          <t>2239-3-LR24</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>70.770.800-K</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3314,43 +3314,43 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>80234.16</v>
+        <v>17483.54</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1087-2-CM26</t>
+          <t>1075963-1737-CM26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2239-13-LR25</t>
+          <t>2239-3-LR24</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3375,43 +3375,43 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>2538.25</v>
+        <v>4640.92</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>516771-4-CM26</t>
+          <t>5358-18-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2239-13-LR25</t>
+          <t>2239-3-LR24</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>60.803.000-k</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3436,13 +3436,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>5768.74</v>
+        <v>9319.120000000001</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>720-36-CM26</t>
+          <t>2366-56-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3457,7 +3457,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3467,12 +3467,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3497,13 +3497,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>4622.35</v>
+        <v>29268.07</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>830715-24-CM26</t>
+          <t>2366-57-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3518,22 +3518,22 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>60.511.139-4</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE PARINACOTA</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3558,13 +3558,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>6036.22</v>
+        <v>34561.97</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1346279-25-CM26</t>
+          <t>1075963-2331-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3579,22 +3579,22 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3619,13 +3619,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>2437.09</v>
+        <v>4602.01</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>4022-95-CM26</t>
+          <t>720-10-CM26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3640,22 +3640,22 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>69.250.800-9</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Putre</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3680,13 +3680,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>23223.68</v>
+        <v>5793.25</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>5857-2-CM26</t>
+          <t>720-11-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3696,27 +3696,27 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>69.251.000-3</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>I.Municipalidad de Camarones</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3741,13 +3741,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>17213.48</v>
+        <v>2781.21</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>635-183-CM26</t>
+          <t>720-12-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>61.606.000-7</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3802,13 +3802,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>7873.7</v>
+        <v>3013.06</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>5855-77-CM26</t>
+          <t>720-9-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3818,27 +3818,27 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>69.251.000-3</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>I.Municipalidad de Camarones</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3863,13 +3863,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>16757.16</v>
+        <v>80234.16</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>3527-42-CM26</t>
+          <t>516771-4-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3879,12 +3879,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>61.101.037-0</t>
+          <t>60.803.000-k</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3924,13 +3924,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>2457.72</v>
+        <v>5768.74</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1075963-3281-CM26</t>
+          <t>1087-2-CM26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3940,27 +3940,27 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3985,13 +3985,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>4420.16</v>
+        <v>2538.25</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>830715-27-CM26</t>
+          <t>720-36-CM26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4001,27 +4001,27 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>60.511.139-4</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE PARINACOTA</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4046,13 +4046,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>5288.34</v>
+        <v>4622.35</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1084148-28-CM26</t>
+          <t>830715-24-CM26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4062,27 +4062,27 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>60.511.139-4</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE PARINACOTA</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4107,13 +4107,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>9763.93</v>
+        <v>6036.22</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1075963-3726-CM26</t>
+          <t>1346279-25-CM26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4123,27 +4123,27 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4168,13 +4168,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>5497.93</v>
+        <v>2437.09</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1572-24-CM26</t>
+          <t>4022-95-CM26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4184,27 +4184,27 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>69.250.800-9</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>Ilustre Municipalidad de Putre</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>3299.93</v>
+        <v>23223.68</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1774-32-CM26</t>
+          <t>5857-2-CM26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4250,22 +4250,22 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>60.804.001-3</t>
+          <t>69.251.000-3</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>ADMINISTRACIÓN ADUANA DE ARICA</t>
+          <t>I.Municipalidad de Camarones</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4290,13 +4290,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>21726.85</v>
+        <v>17213.48</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1075963-4041-CM26</t>
+          <t>635-183-CM26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4311,22 +4311,22 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>61.606.000-7</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4351,13 +4351,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>3264.15</v>
+        <v>7873.7</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>5702-204-CM26</t>
+          <t>5855-77-CM26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4372,22 +4372,22 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>69.251.000-3</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>I.Municipalidad de Camarones</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4412,13 +4412,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>5459.95</v>
+        <v>16757.16</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1087-50-CM26</t>
+          <t>3527-42-CM26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4433,7 +4433,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.101.037-0</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4473,13 +4473,13 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>4301.54</v>
+        <v>2457.72</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>830715-31-CM26</t>
+          <t>1075963-3281-CM26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4504,12 +4504,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>60.511.139-4</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE PARINACOTA</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4534,13 +4534,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>8540.17</v>
+        <v>4420.16</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>720-97-CM26</t>
+          <t>1084148-28-CM26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4555,7 +4555,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4565,12 +4565,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4595,13 +4595,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>73348.14999999999</v>
+        <v>9763.93</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>720-98-CM26</t>
+          <t>830715-27-CM26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4616,22 +4616,22 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>60.511.139-4</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE PARINACOTA</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4656,13 +4656,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>18394.45</v>
+        <v>5288.34</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>5855-105-CM26</t>
+          <t>1075963-3726-CM26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4672,12 +4672,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4687,12 +4687,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>69.251.000-3</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>I.Municipalidad de Camarones</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4717,13 +4717,13 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>83211.14</v>
+        <v>5497.93</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>5855-106-CM26</t>
+          <t>1572-24-CM26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4733,27 +4733,27 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>69.251.000-3</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>I.Municipalidad de Camarones</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4778,13 +4778,13 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>77965.63</v>
+        <v>3299.93</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>1087-51-CM26</t>
+          <t>1774-32-CM26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4794,12 +4794,12 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>60.804.001-3</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>ADMINISTRACIÓN ADUANA DE ARICA</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4839,13 +4839,13 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>2293.79</v>
+        <v>21726.85</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>635-353-CM26</t>
+          <t>1075963-4041-CM26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4855,27 +4855,27 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>61.606.000-7</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4900,13 +4900,13 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>32805.89</v>
+        <v>3264.15</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>963423-62-CM26</t>
+          <t>5702-204-CM26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4916,12 +4916,12 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4931,12 +4931,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>61.980.850-9</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Zona de Bienestar Arica</t>
+          <t>Direc.Reg.Arica y Parinacota</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4961,13 +4961,13 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>3117.95</v>
+        <v>5459.95</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>1075963-4970-CM26</t>
+          <t>1087-50-CM26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4977,27 +4977,27 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5022,13 +5022,13 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>5350.82</v>
+        <v>4301.54</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>5611-34-CM26</t>
+          <t>830715-31-CM26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5038,27 +5038,27 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>61.813.000-2</t>
+          <t>60.511.139-4</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>SERVICIO REGIONAL DE LA VIVIENDA Y URBAN</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE PARINACOTA</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5083,13 +5083,13 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>6671.19</v>
+        <v>8540.17</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>1087-68-CM26</t>
+          <t>720-97-CM26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -5114,12 +5114,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5144,13 +5144,13 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>3382.3</v>
+        <v>73348.14999999999</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2021-74-CM26</t>
+          <t>720-98-CM26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5160,12 +5160,12 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -5175,12 +5175,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>61.101.040-0</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Estado Mayor Conjunto</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5205,13 +5205,13 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>10156.98</v>
+        <v>18394.45</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>1075963-5216-CM26</t>
+          <t>5855-105-CM26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5226,22 +5226,22 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>69.251.000-3</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>I.Municipalidad de Camarones</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5266,13 +5266,13 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>9146.93</v>
+        <v>83211.14</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2366-250-CM26</t>
+          <t>5855-106-CM26</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5287,22 +5287,22 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>69.251.000-3</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>I.Municipalidad de Camarones</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5327,13 +5327,13 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>32392.28</v>
+        <v>77965.63</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2585-267-CM26</t>
+          <t>1087-51-CM26</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5348,7 +5348,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -5358,12 +5358,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5388,13 +5388,13 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>22695.81</v>
+        <v>2293.79</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>5702-283-CM26</t>
+          <t>635-353-CM26</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5409,7 +5409,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -5419,12 +5419,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>61.606.000-7</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5449,13 +5449,13 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>2921.78</v>
+        <v>32805.89</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>830715-33-CM26</t>
+          <t>963423-62-CM26</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5470,22 +5470,22 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>60.511.139-4</t>
+          <t>61.980.850-9</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE PARINACOTA</t>
+          <t>Zona de Bienestar Arica</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5510,13 +5510,13 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>9316.59</v>
+        <v>3117.95</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>1346279-44-CM26</t>
+          <t>1075963-4970-CM26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5531,22 +5531,22 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>4026.04</v>
+        <v>5350.82</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>5358-93-CM26</t>
+          <t>5611-34-CM26</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5592,22 +5592,22 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>61.813.000-2</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>SERVICIO REGIONAL DE LA VIVIENDA Y URBAN</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5632,13 +5632,13 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>11048.74</v>
+        <v>6671.19</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>5622-10-CM26</t>
+          <t>1087-68-CM26</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5653,7 +5653,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -5663,12 +5663,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>61.979.000-6</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Pesca y Acuicultura</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5693,13 +5693,13 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>2343.67</v>
+        <v>3382.3</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>1093870-3-CM26</t>
+          <t>1075963-5216-CM26</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5714,7 +5714,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5724,12 +5724,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>65.184.303-0</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE EDUCACION SUPERIOR</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5754,13 +5754,13 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>6653.66</v>
+        <v>9146.93</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>4022-244-CM26</t>
+          <t>2021-74-CM26</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5770,27 +5770,27 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>69.250.800-9</t>
+          <t>61.101.040-0</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Putre</t>
+          <t>Estado Mayor Conjunto</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -5815,13 +5815,13 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>22400.68</v>
+        <v>10156.98</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>1087-96-CM26</t>
+          <t>2366-250-CM26</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5831,12 +5831,12 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -5846,12 +5846,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -5876,13 +5876,13 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>2693.68</v>
+        <v>32392.28</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>720-103-CM26</t>
+          <t>2585-267-CM26</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5892,12 +5892,12 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -5907,12 +5907,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -5937,13 +5937,13 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>77431.35000000001</v>
+        <v>22695.81</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>1443565-16-CM26</t>
+          <t>5702-283-CM26</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5953,27 +5953,27 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>61.312.000-9</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>INSTITUTO DE INVESTIGACIONES AGROPECUARIAS</t>
+          <t>Direc.Reg.Arica y Parinacota</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -5998,13 +5998,13 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>3011.41</v>
+        <v>2921.78</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>941739-38-CM26</t>
+          <t>830715-33-CM26</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -6029,12 +6029,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>70.770.800-K</t>
+          <t>60.511.139-4</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE PARINACOTA</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6059,13 +6059,13 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>19079.69</v>
+        <v>9316.59</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>1075963-6508-CM26</t>
+          <t>1346279-44-CM26</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6075,27 +6075,27 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>5303.03</v>
+        <v>4026.04</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>5702-350-CM26</t>
+          <t>5358-93-CM26</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6136,27 +6136,27 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6181,13 +6181,13 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>2754.79</v>
+        <v>11048.74</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>635-642-CM26</t>
+          <t>5622-10-CM26</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -6212,12 +6212,12 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>61.606.000-7</t>
+          <t>61.979.000-6</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
+          <t>Servicio Nacional de Pesca y Acuicultura</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6242,13 +6242,13 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>8941.84</v>
+        <v>2343.67</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>1087-115-CM26</t>
+          <t>1093870-3-CM26</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -6273,12 +6273,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>65.184.303-0</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>SUBSECRETARIA DE EDUCACION SUPERIOR</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6303,13 +6303,13 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>8794.24</v>
+        <v>6653.66</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>5702-380-CM26</t>
+          <t>4022-244-CM26</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6319,27 +6319,27 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>69.250.800-9</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>Ilustre Municipalidad de Putre</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6364,13 +6364,13 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>2799.83</v>
+        <v>22400.68</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>720-153-CM26</t>
+          <t>1087-96-CM26</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6380,12 +6380,12 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -6395,12 +6395,12 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6425,13 +6425,13 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>62497.17</v>
+        <v>2693.68</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2021-111-CM26</t>
+          <t>720-103-CM26</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6441,12 +6441,12 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>61.101.040-0</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Estado Mayor Conjunto</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>EMPRESA NACIONAL DE ENERGIA ENEX S.A.</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>92.011.000-2</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K99" t="inlineStr"/>
@@ -6486,13 +6486,13 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>6089.45</v>
+        <v>77431.35000000001</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>1075963-7514-CM26</t>
+          <t>1443565-16-CM26</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6502,12 +6502,12 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -6517,12 +6517,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>61.312.000-9</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>INSTITUTO DE INVESTIGACIONES AGROPECUARIAS</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6547,13 +6547,13 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>6779.96</v>
+        <v>3011.41</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>696027-27-CM26</t>
+          <t>1075963-6508-CM26</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6563,12 +6563,12 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -6578,12 +6578,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>4352.98</v>
+        <v>5303.03</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>5667-67-CM26</t>
+          <t>941739-38-CM26</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>61.979.080-4</t>
+          <t>70.770.800-K</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>SEREMI de Educación Arica y Parinacota</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6669,13 +6669,13 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>2347.24</v>
+        <v>19079.69</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>1087-130-CM26</t>
+          <t>5702-350-CM26</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6685,12 +6685,12 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>Direc.Reg.Arica y Parinacota</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -6730,13 +6730,13 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>2816.97</v>
+        <v>2754.79</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>5702-427-CM26</t>
+          <t>635-642-CM26</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6746,12 +6746,12 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>61.606.000-7</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -6791,13 +6791,13 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>2808.58</v>
+        <v>8941.84</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>5702-428-CM26</t>
+          <t>1087-115-CM26</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6807,12 +6807,12 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -6822,12 +6822,12 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -6852,13 +6852,13 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>2808.58</v>
+        <v>8794.24</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>1337362-33-CM26</t>
+          <t>5702-380-CM26</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6873,7 +6873,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -6883,12 +6883,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL DE ARICA Y PARINACOTA</t>
+          <t>Direc.Reg.Arica y Parinacota</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -6913,13 +6913,13 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>2425.19</v>
+        <v>2799.83</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>720-165-CM26</t>
+          <t>720-153-CM26</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6934,7 +6934,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -6974,13 +6974,13 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>7321.46</v>
+        <v>62497.17</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>4022-333-CM26</t>
+          <t>2021-111-CM26</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -6995,22 +6995,22 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>69.250.800-9</t>
+          <t>61.101.040-0</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Putre</t>
+          <t>Estado Mayor Conjunto</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -7020,12 +7020,12 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>EMPRESA NACIONAL DE ENERGIA ENEX S.A.</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>92.011.000-2</t>
         </is>
       </c>
       <c r="K108" t="inlineStr"/>
@@ -7035,13 +7035,13 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>22638.26</v>
+        <v>6089.45</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>509920-5-CM26</t>
+          <t>1075963-7514-CM26</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7056,7 +7056,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Servicio Nacional del Patrimonio Cultural</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -7096,13 +7096,13 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>2433.61</v>
+        <v>6779.96</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>5667-72-CM26</t>
+          <t>696027-27-CM26</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7117,22 +7117,22 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>61.979.080-4</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>SEREMI de Educación Arica y Parinacota</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7157,13 +7157,13 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>2387.3</v>
+        <v>4352.98</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>1087-139-CM26</t>
+          <t>5667-67-CM26</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7178,22 +7178,22 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.979.080-4</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>SEREMI de Educación Arica y Parinacota</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7218,13 +7218,13 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>3312.06</v>
+        <v>2347.24</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>1075963-8208-CM26</t>
+          <t>1087-130-CM26</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7239,22 +7239,22 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7279,13 +7279,13 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>4590.53</v>
+        <v>2816.97</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2369-67-CM26</t>
+          <t>5702-427-CM26</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7300,22 +7300,22 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>Direc.Reg.Arica y Parinacota</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -7325,32 +7325,28 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
-        </is>
-      </c>
-      <c r="K113" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Región de Atacama </t>
-        </is>
-      </c>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr"/>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>0</v>
+        <v>2808.58</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>1774-74-CM26</t>
+          <t>5702-428-CM26</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7365,7 +7361,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -7375,12 +7371,12 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>60.804.001-3</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>ADMINISTRACIÓN ADUANA DE ARICA</t>
+          <t>Direc.Reg.Arica y Parinacota</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7405,13 +7401,13 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>5044.46</v>
+        <v>2808.58</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>696027-35-CM26</t>
+          <t>1337362-33-CM26</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7426,22 +7422,22 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>DIRECCIÓN REGIONAL DE ARICA Y PARINACOTA</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7466,13 +7462,13 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>6658.05</v>
+        <v>2425.19</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>1075963-8659-CM26</t>
+          <t>509920-5-CM26</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7482,12 +7478,12 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -7497,12 +7493,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>Servicio Nacional del Patrimonio Cultural</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7527,13 +7523,13 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>5287.65</v>
+        <v>2433.61</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>1075963-8732-CM26</t>
+          <t>4022-333-CM26</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7543,27 +7539,27 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>69.250.800-9</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>Ilustre Municipalidad de Putre</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -7588,13 +7584,13 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>7594.66</v>
+        <v>22638.26</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>720-155-CM26</t>
+          <t>720-165-CM26</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7604,12 +7600,12 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -7649,13 +7645,13 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>7742.83</v>
+        <v>7321.46</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2366-434-CM26</t>
+          <t>5667-72-CM26</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7665,12 +7661,12 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -7680,12 +7676,12 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.979.080-4</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SEREMI de Educación Arica y Parinacota</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -7710,13 +7706,13 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>34438.48</v>
+        <v>2387.3</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>5857-25-CM26</t>
+          <t>1087-139-CM26</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7726,27 +7722,27 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>69.251.000-3</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>I.Municipalidad de Camarones</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -7771,13 +7767,13 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>25361.43</v>
+        <v>3312.06</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>720-224-CM26</t>
+          <t>1075963-8208-CM26</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -7787,27 +7783,27 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -7832,13 +7828,13 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>35793.31</v>
+        <v>4590.53</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>5702-506-CM26</t>
+          <t>2369-67-CM26</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -7848,27 +7844,27 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -7878,28 +7874,32 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
-        </is>
-      </c>
-      <c r="K122" t="inlineStr"/>
+          <t>79.588.870-5</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Atacama </t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>2703.35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>1075963-9267-CM26</t>
+          <t>1774-74-CM26</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -7909,27 +7909,27 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>60.804.001-3</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>ADMINISTRACIÓN ADUANA DE ARICA</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -7954,13 +7954,13 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>4715.72</v>
+        <v>5044.46</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>5702-526-CM26</t>
+          <t>696027-35-CM26</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -7970,27 +7970,27 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -8015,13 +8015,13 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>4756.17</v>
+        <v>6658.05</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>4022-381-CM26</t>
+          <t>1075963-8659-CM26</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -8046,12 +8046,12 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>69.250.800-9</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Putre</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -8076,6 +8076,555 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
+        <v>5287.65</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>1075963-8732-CM26</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>61.606.001-5</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M126" s="2" t="n">
+        <v>7594.66</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>720-155-CM26</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>61.308.000-7</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M127" s="2" t="n">
+        <v>7742.83</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2366-434-CM26</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>69.010.100-9</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ARICA</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M128" s="2" t="n">
+        <v>34438.48</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>5857-25-CM26</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>69.251.000-3</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>I.Municipalidad de Camarones</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M129" s="2" t="n">
+        <v>25361.43</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>720-224-CM26</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>61.308.000-7</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M130" s="2" t="n">
+        <v>35793.31</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>5702-506-CM26</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>61.979.020-0</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Direc.Reg.Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M131" s="2" t="n">
+        <v>2703.35</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>1075963-9267-CM26</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>61.606.001-5</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M132" s="2" t="n">
+        <v>4715.72</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>5702-526-CM26</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>61.979.020-0</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Direc.Reg.Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M133" s="2" t="n">
+        <v>4756.17</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>4022-381-CM26</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>69.250.800-9</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Ilustre Municipalidad de Putre</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr"/>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M134" s="2" t="n">
         <v>21233</v>
       </c>
     </row>

--- a/docs/oc-regiones/suministro-de-combustibles/arica-y-parinacota.xlsx
+++ b/docs/oc-regiones/suministro-de-combustibles/arica-y-parinacota.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M291"/>
+  <dimension ref="A1:M298"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -666,7 +666,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>COMANDO DE APOYO A LA FUERZA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1429,7 +1429,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>801-7-CM25</t>
+          <t>941739-11-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1449,17 +1449,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>72.396.000-2</t>
+          <t>70.770.800-K</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>2090.76</v>
+        <v>20669.91</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>941739-11-CM25</t>
+          <t>801-7-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1510,17 +1510,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>70.770.800-K</t>
+          <t>72.396.000-2</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>20669.91</v>
+        <v>2090.76</v>
       </c>
     </row>
     <row r="19">
@@ -1856,7 +1856,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2202-198-CM25</t>
+          <t>1075963-7128-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1876,17 +1876,17 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>61.602.241-5</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ARAUCANIA NORTE HOSPITAL CURACAUTIN</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>4224.04</v>
+        <v>3418.31</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1075963-7128-CM25</t>
+          <t>2202-198-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1937,17 +1937,17 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>61.602.241-5</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>SERVICIO SALUD ARAUCANIA NORTE HOSPITAL CURACAUTIN</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>3418.31</v>
+        <v>4224.04</v>
       </c>
     </row>
     <row r="26">
@@ -2405,7 +2405,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>5611-21-CM25</t>
+          <t>5855-64-CM25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2430,12 +2430,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>61.813.000-2</t>
+          <t>69.251.000-3</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>SERVICIO REGIONAL DE LA VIVIENDA Y URBAN</t>
+          <t>Ilustre Municipalidad de Camarones</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2460,13 +2460,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>3075.26</v>
+        <v>32179.17</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>5855-64-CM25</t>
+          <t>5611-21-CM25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2491,12 +2491,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>69.251.000-3</t>
+          <t>61.813.000-2</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Camarones</t>
+          <t>SERVICIO REGIONAL DE LA VIVIENDA Y URBAN</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2521,13 +2521,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>32179.17</v>
+        <v>3075.26</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>720-95-CM25</t>
+          <t>1075963-15057-CM25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2547,17 +2547,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2582,13 +2582,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>71261.42999999999</v>
+        <v>3372.69</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1075963-15057-CM25</t>
+          <t>720-95-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2608,17 +2608,17 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>3372.69</v>
+        <v>71261.42999999999</v>
       </c>
     </row>
     <row r="37">
@@ -3808,7 +3808,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>830715-33-CM25</t>
+          <t>1084148-70-CM25</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3828,17 +3828,17 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>60.511.139-4</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE PARINACOTA</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>5766.45</v>
+        <v>2233.61</v>
       </c>
     </row>
     <row r="57">
@@ -3930,7 +3930,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1084148-70-CM25</t>
+          <t>4022-278-CM25</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3950,17 +3950,17 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>69.250.800-9</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PUTRE</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3985,13 +3985,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>2233.61</v>
+        <v>21272.52</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>4022-278-CM25</t>
+          <t>830715-33-CM25</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4016,12 +4016,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>69.250.800-9</t>
+          <t>60.511.139-4</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE PUTRE</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE PARINACOTA</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>21272.52</v>
+        <v>5766.45</v>
       </c>
     </row>
     <row r="60">
@@ -4235,7 +4235,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1774-78-CM25</t>
+          <t>720-210-CM25</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4260,12 +4260,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>60.804.001-3</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE ADUANAS</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4290,13 +4290,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>11899.7</v>
+        <v>10093.5</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>720-210-CM25</t>
+          <t>720-213-CM25</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>10093.5</v>
+        <v>65873.77</v>
       </c>
     </row>
     <row r="65">
@@ -4418,7 +4418,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>720-213-CM25</t>
+          <t>1774-78-CM25</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>60.804.001-3</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>65873.77</v>
+        <v>11899.7</v>
       </c>
     </row>
     <row r="67">
@@ -4601,7 +4601,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>838099-49-CM25</t>
+          <t>2585-3560-CM25</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4626,12 +4626,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>73.923.800-5</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4656,13 +4656,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>6394.68</v>
+        <v>72473.03999999999</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2585-3560-CM25</t>
+          <t>5358-155-CM25</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4687,12 +4687,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4717,13 +4717,13 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>72473.03999999999</v>
+        <v>4902.59</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>5358-155-CM25</t>
+          <t>1110404-471-CM25</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4778,13 +4778,13 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>4902.59</v>
+        <v>70341.48</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>1110404-471-CM25</t>
+          <t>838099-49-CM25</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>73.923.800-5</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>70341.48</v>
+        <v>6394.68</v>
       </c>
     </row>
     <row r="73">
@@ -5394,7 +5394,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1075963-21457-CM25</t>
+          <t>1774-96-CM25</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5414,17 +5414,17 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>60.804.001-3</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5449,13 +5449,13 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>3220.67</v>
+        <v>7484.95</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>1774-96-CM25</t>
+          <t>1075963-21457-CM25</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5475,17 +5475,17 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>60.804.001-3</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE ADUANAS</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>7484.95</v>
+        <v>3220.67</v>
       </c>
     </row>
     <row r="84">
@@ -5943,7 +5943,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>1346279-122-CM25</t>
+          <t>5702-509-CM25</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -6004,7 +6004,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>5702-509-CM25</t>
+          <t>1346279-122-CM25</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6029,12 +6029,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6492,7 +6492,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>1572-266-CM25</t>
+          <t>1075963-23029-CM25</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6512,17 +6512,17 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6547,13 +6547,13 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>2505.69</v>
+        <v>6880.21</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>1075963-23029-CM25</t>
+          <t>1572-266-CM25</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6573,17 +6573,17 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>6880.21</v>
+        <v>2505.69</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>720-352-CM25</t>
+          <t>5952-239-CM25</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6634,17 +6634,17 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6669,13 +6669,13 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>70121.09</v>
+        <v>4124.77</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>5952-239-CM25</t>
+          <t>720-352-CM25</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6695,17 +6695,17 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -6730,7 +6730,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>4124.77</v>
+        <v>70121.09</v>
       </c>
     </row>
     <row r="104">
@@ -7590,7 +7590,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>5358-309-CM25</t>
+          <t>963423-2640-CM25</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>61.980.850-9</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -7645,13 +7645,13 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>2581.71</v>
+        <v>2168.64</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>963423-2640-CM25</t>
+          <t>5358-309-CM25</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7676,12 +7676,12 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>61.980.850-9</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -7706,13 +7706,13 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>2168.64</v>
+        <v>2581.71</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>3527-258-CM25</t>
+          <t>1075963-24769-CM25</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7732,17 +7732,17 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>61.101.037-0</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -7767,13 +7767,13 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>2977.02</v>
+        <v>4282.8</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>1075963-24769-CM25</t>
+          <t>3527-258-CM25</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -7793,17 +7793,17 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>61.101.037-0</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -7828,7 +7828,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>4282.8</v>
+        <v>2977.02</v>
       </c>
     </row>
     <row r="122">
@@ -7895,7 +7895,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>5702-715-CM25</t>
+          <t>5702-716-CM25</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -7956,7 +7956,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>5702-716-CM25</t>
+          <t>5702-715-CM25</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -8139,7 +8139,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>720-450-CM25</t>
+          <t>720-446-CM25</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8194,13 +8194,13 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>2518.18</v>
+        <v>9969.52</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>720-446-CM25</t>
+          <t>720-449-CM25</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8255,13 +8255,13 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>9969.52</v>
+        <v>2203.87</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>720-449-CM25</t>
+          <t>720-450-CM25</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8316,7 +8316,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>2203.87</v>
+        <v>2518.18</v>
       </c>
     </row>
     <row r="130">
@@ -8383,7 +8383,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>5358-343-CM25</t>
+          <t>5667-205-CM25</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8403,17 +8403,17 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>61.979.080-4</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -8438,13 +8438,13 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>6257.17</v>
+        <v>2607.15</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>5667-205-CM25</t>
+          <t>5358-343-CM25</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8464,17 +8464,17 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>61.979.080-4</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>2607.15</v>
+        <v>6257.17</v>
       </c>
     </row>
     <row r="133">
@@ -8871,7 +8871,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>5855-274-CM25</t>
+          <t>5857-55-CM25</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -8926,13 +8926,13 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>31434.35</v>
+        <v>12573.74</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>5857-55-CM25</t>
+          <t>5855-274-CM25</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -8987,13 +8987,13 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>12573.74</v>
+        <v>31434.35</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>1346279-190-CM25</t>
+          <t>5855-275-CM25</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -9018,12 +9018,12 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>69.251.000-3</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>Ilustre Municipalidad de Camarones</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -9048,13 +9048,13 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>2192.85</v>
+        <v>31326.36</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>5649-27-CM25</t>
+          <t>1346279-190-CM25</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -9074,17 +9074,17 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>61.979.030-8</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>MINISTERIO DE BIENES NACIONALES</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -9109,13 +9109,13 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>2245.06</v>
+        <v>2192.85</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>5855-275-CM25</t>
+          <t>5649-27-CM25</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -9135,17 +9135,17 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>69.251.000-3</t>
+          <t>61.979.030-8</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Camarones</t>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -9170,7 +9170,7 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>31326.36</v>
+        <v>2245.06</v>
       </c>
     </row>
     <row r="144">
@@ -9420,7 +9420,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>5792-23-CM25</t>
+          <t>720-496-CM25</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -9445,12 +9445,12 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>61.702.000-9</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE GEOLOGIA Y MINERIA</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -9475,13 +9475,13 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>2644.55</v>
+        <v>73269.92999999999</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>5622-34-CM25</t>
+          <t>5792-23-CM25</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -9506,12 +9506,12 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>61.979.000-6</t>
+          <t>61.702.000-9</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>SERV NACIONAL DE PESCA</t>
+          <t>SERVICIO NACIONAL DE GEOLOGIA Y MINERIA</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -9536,13 +9536,13 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>2198.1</v>
+        <v>2644.55</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>720-496-CM25</t>
+          <t>5622-34-CM25</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -9567,12 +9567,12 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.979.000-6</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>SERV NACIONAL DE PESCA</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -9597,7 +9597,7 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>73269.92999999999</v>
+        <v>2198.1</v>
       </c>
     </row>
     <row r="151">
@@ -9725,7 +9725,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>5420-295-CM25</t>
+          <t>5420-296-CM25</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -9780,13 +9780,13 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>6379.11</v>
+        <v>4252.74</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>5420-296-CM25</t>
+          <t>5420-295-CM25</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -9841,7 +9841,7 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>4252.74</v>
+        <v>6379.11</v>
       </c>
     </row>
     <row r="155">
@@ -10182,7 +10182,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Putre</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PUTRE</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -10243,7 +10243,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -10274,7 +10274,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>978-272-CM25</t>
+          <t>4022-804-CM25</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -10289,22 +10289,22 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.250.800-9</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PUTRE</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -10329,13 +10329,13 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>21336.52</v>
+        <v>21286.33</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>4022-804-CM25</t>
+          <t>720-1088-CM25</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -10350,22 +10350,22 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>69.250.800-9</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Putre</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -10390,13 +10390,13 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>21286.33</v>
+        <v>15407.52</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>720-1088-CM25</t>
+          <t>720-479-CM25</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -10411,7 +10411,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -10451,13 +10451,13 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>15407.52</v>
+        <v>11816.65</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>720-479-CM25</t>
+          <t>1774-236-CM25</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -10472,7 +10472,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -10482,12 +10482,12 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>60.804.001-3</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -10512,13 +10512,13 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>11816.65</v>
+        <v>4089.8</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>5702-916-CM25</t>
+          <t>720-1096-CM25</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -10543,12 +10543,12 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -10573,13 +10573,13 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>2690.66</v>
+        <v>45203.09</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>1774-236-CM25</t>
+          <t>5702-916-CM25</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -10604,12 +10604,12 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>60.804.001-3</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>ADMINISTRACIÓN ADUANA DE ARICA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -10634,13 +10634,13 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>4089.8</v>
+        <v>2690.66</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>720-1096-CM25</t>
+          <t>3527-339-CM25</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -10650,12 +10650,12 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -10665,12 +10665,12 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.101.037-0</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -10695,13 +10695,13 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>45203.09</v>
+        <v>27027.32</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>3527-339-CM25</t>
+          <t>548849-100-CM25</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -10716,7 +10716,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -10726,12 +10726,12 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>61.101.037-0</t>
+          <t>61.979.440-0</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>INSTITUTO DE PREVISION SOCIAL</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -10756,13 +10756,13 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>27027.32</v>
+        <v>3890.34</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>548849-100-CM25</t>
+          <t>3527-344-CM25</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>61.979.440-0</t>
+          <t>61.101.037-0</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Instituto de Prevision Social</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -10817,13 +10817,13 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>3890.34</v>
+        <v>2377.43</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>3527-344-CM25</t>
+          <t>5648-75-CM25</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -10838,7 +10838,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -10848,12 +10848,12 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>61.101.037-0</t>
+          <t>61.979.070-7</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -10878,13 +10878,13 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>2377.43</v>
+        <v>2392.71</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>5648-75-CM25</t>
+          <t>2202-1094-CM25</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -10899,7 +10899,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -10909,12 +10909,12 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>61.979.070-7</t>
+          <t>61.602.241-5</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Ministerio de Vivienda y Urbanismo</t>
+          <t>SERVICIO SALUD ARAUCANIA NORTE HOSPITAL CURACAUTIN</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -10939,7 +10939,7 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>2392.71</v>
+        <v>4356.59</v>
       </c>
     </row>
     <row r="173">
@@ -11097,7 +11097,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Zona Bienestar "Arica" Bienestar Social</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -11128,7 +11128,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>1606-586-CM25</t>
+          <t>1087-386-CM25</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -11143,7 +11143,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -11153,12 +11153,12 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>60.108.000-1</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>AGENCIA CHILENA DE COOPERACION INTERNACIONAL PARA EL DESARROLLO</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -11183,13 +11183,13 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>3269.93</v>
+        <v>7693.15</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>1087-386-CM25</t>
+          <t>5667-318-CM25</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -11204,7 +11204,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -11214,12 +11214,12 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.979.080-4</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -11244,13 +11244,13 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>7693.15</v>
+        <v>2297.45</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>5667-318-CM25</t>
+          <t>5702-964-CM25</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -11275,12 +11275,12 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>61.979.080-4</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>SEREMI de Educación Arica y Parinacota</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -11305,13 +11305,13 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>2297.45</v>
+        <v>4953.76</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>5702-964-CM25</t>
+          <t>1075963-61121-CM25</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -11331,17 +11331,17 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -11366,13 +11366,13 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>4953.76</v>
+        <v>3394.98</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>1075963-61121-CM25</t>
+          <t>720-1182-CM25</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -11387,22 +11387,22 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-27</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -11427,13 +11427,13 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>3394.98</v>
+        <v>11137.93</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>978-299-CM25</t>
+          <t>5702-978-CM25</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -11448,7 +11448,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>66050.2</v>
+        <v>3316.6</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>720-1182-CM25</t>
+          <t>1110404-1633-CM25</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -11509,7 +11509,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -11519,12 +11519,12 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -11549,13 +11549,13 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>11137.93</v>
+        <v>2321.62</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>1110404-1633-CM25</t>
+          <t>1075963-90-CM26</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -11565,27 +11565,27 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -11610,13 +11610,13 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>2321.62</v>
+        <v>4531.57</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>5702-978-CM25</t>
+          <t>1232837-29-CM26</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -11626,12 +11626,12 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -11641,12 +11641,12 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>65.166.511-6</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>CORPORACION MUNICIPAL DE FOMENTO   PRODUCTIVO DE ARICA</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -11671,13 +11671,13 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>3316.6</v>
+        <v>2810.44</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>978-301-CM25</t>
+          <t>1489-2-CM26</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -11687,12 +11687,12 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -11702,12 +11702,12 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.979.110-k</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -11732,13 +11732,13 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>3292.43</v>
+        <v>4586</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>1075963-90-CM26</t>
+          <t>830715-2-CM26</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -11753,7 +11753,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>60.511.139-4</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE PARINACOTA</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -11793,13 +11793,13 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>4531.57</v>
+        <v>6066.31</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2021-3-CM26</t>
+          <t>941739-7-CM26</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -11814,22 +11814,22 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>61.101.040-0</t>
+          <t>70.770.800-K</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Estado Mayor Conjunto</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -11854,13 +11854,13 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>5636.92</v>
+        <v>17483.54</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>1232837-29-CM26</t>
+          <t>1075963-1737-CM26</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -11875,22 +11875,22 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>65.166.511-6</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE FOMENTO   PRODUCTIVO DE ARICA</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -11915,13 +11915,13 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>2810.44</v>
+        <v>4640.92</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>1489-2-CM26</t>
+          <t>5358-18-CM26</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -11936,22 +11936,22 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>61.979.110-k</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>SERPLAC ARICA Y PARINACOTA</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -11976,43 +11976,43 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>4586</v>
+        <v>9319.120000000001</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>830715-2-CM26</t>
+          <t>2366-57-CM26</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2239-3-LR24</t>
+          <t>2239-13-LR25</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>60.511.139-4</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE PARINACOTA</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -12037,43 +12037,43 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>6066.31</v>
+        <v>34561.97</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>941739-7-CM26</t>
+          <t>2366-56-CM26</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2239-3-LR24</t>
+          <t>2239-13-LR25</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>70.770.800-K</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -12098,28 +12098,28 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>17483.54</v>
+        <v>29268.07</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>5358-18-CM26</t>
+          <t>1075963-2331-CM26</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2239-3-LR24</t>
+          <t>2239-13-LR25</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -12129,12 +12129,12 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -12159,43 +12159,43 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>9319.120000000001</v>
+        <v>4602.01</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>1075963-1737-CM26</t>
+          <t>720-10-CM26</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2239-3-LR24</t>
+          <t>2239-13-LR25</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -12220,13 +12220,13 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>4640.92</v>
+        <v>5793.25</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2366-56-CM26</t>
+          <t>720-11-CM26</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -12241,7 +12241,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -12251,12 +12251,12 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -12281,13 +12281,13 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>29268.07</v>
+        <v>2781.21</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2366-57-CM26</t>
+          <t>720-12-CM26</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -12302,7 +12302,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -12312,12 +12312,12 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -12342,13 +12342,13 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>34561.97</v>
+        <v>3013.06</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>1075963-2331-CM26</t>
+          <t>720-9-CM26</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -12363,22 +12363,22 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -12403,13 +12403,13 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>4602.01</v>
+        <v>80234.16</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>720-10-CM26</t>
+          <t>1087-2-CM26</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -12424,7 +12424,7 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -12434,12 +12434,12 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -12464,13 +12464,13 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>5793.25</v>
+        <v>2538.25</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>720-11-CM26</t>
+          <t>720-36-CM26</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -12485,7 +12485,7 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -12525,13 +12525,13 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>2781.21</v>
+        <v>4622.35</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>720-12-CM26</t>
+          <t>830715-24-CM26</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -12546,22 +12546,22 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>60.511.139-4</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE PARINACOTA</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -12586,13 +12586,13 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>3013.06</v>
+        <v>6036.22</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>720-9-CM26</t>
+          <t>1346279-25-CM26</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -12607,7 +12607,7 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -12617,12 +12617,12 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -12647,13 +12647,13 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>80234.16</v>
+        <v>2437.09</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>1087-2-CM26</t>
+          <t>4022-95-CM26</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -12668,22 +12668,22 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.250.800-9</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PUTRE</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -12708,13 +12708,13 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>2538.25</v>
+        <v>23223.68</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>516771-4-CM26</t>
+          <t>5857-2-CM26</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -12724,27 +12724,27 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>60.803.000-k</t>
+          <t>69.251.000-3</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
+          <t>Ilustre Municipalidad de Camarones</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -12769,13 +12769,13 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>5768.74</v>
+        <v>17213.48</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>830715-24-CM26</t>
+          <t>635-183-CM26</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -12785,27 +12785,27 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>60.511.139-4</t>
+          <t>61.606.000-7</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE PARINACOTA</t>
+          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -12830,13 +12830,13 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>6036.22</v>
+        <v>7873.7</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>720-36-CM26</t>
+          <t>5855-77-CM26</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -12846,27 +12846,27 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>69.251.000-3</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>Ilustre Municipalidad de Camarones</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -12891,13 +12891,13 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>4622.35</v>
+        <v>16757.16</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>1346279-25-CM26</t>
+          <t>3527-42-CM26</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -12907,12 +12907,12 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -12922,12 +12922,12 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.101.037-0</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -12952,13 +12952,13 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>2437.09</v>
+        <v>2457.72</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>4022-95-CM26</t>
+          <t>1075963-3281-CM26</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -12968,12 +12968,12 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -12983,12 +12983,12 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>69.250.800-9</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Putre</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -13013,13 +13013,13 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>23223.68</v>
+        <v>4420.16</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>5857-2-CM26</t>
+          <t>830715-27-CM26</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -13034,7 +13034,7 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
@@ -13044,12 +13044,12 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>69.251.000-3</t>
+          <t>60.511.139-4</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>I.Municipalidad de Camarones</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE PARINACOTA</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -13074,13 +13074,13 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>17213.48</v>
+        <v>5288.34</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>635-183-CM26</t>
+          <t>1084148-28-CM26</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -13095,7 +13095,7 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
@@ -13105,12 +13105,12 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>61.606.000-7</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -13135,13 +13135,13 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>7873.7</v>
+        <v>9763.93</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>5855-77-CM26</t>
+          <t>1075963-3726-CM26</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -13156,7 +13156,7 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -13166,12 +13166,12 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>69.251.000-3</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>I.Municipalidad de Camarones</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -13196,13 +13196,13 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>16757.16</v>
+        <v>5497.93</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>3527-42-CM26</t>
+          <t>1572-24-CM26</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -13217,7 +13217,7 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -13227,12 +13227,12 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>61.101.037-0</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -13257,13 +13257,13 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>2457.72</v>
+        <v>3299.93</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>1075963-3281-CM26</t>
+          <t>1774-32-CM26</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -13278,22 +13278,22 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>60.804.001-3</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -13318,13 +13318,13 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>4420.16</v>
+        <v>21726.85</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>830715-27-CM26</t>
+          <t>1075963-4041-CM26</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -13339,7 +13339,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -13349,12 +13349,12 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>60.511.139-4</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE PARINACOTA</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -13379,13 +13379,13 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>5288.34</v>
+        <v>3264.15</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>1084148-28-CM26</t>
+          <t>5702-204-CM26</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -13400,7 +13400,7 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -13410,12 +13410,12 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -13440,13 +13440,13 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>9763.93</v>
+        <v>5459.95</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>1075963-3726-CM26</t>
+          <t>1087-50-CM26</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -13461,22 +13461,22 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -13501,13 +13501,13 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>5497.93</v>
+        <v>4301.54</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>1572-24-CM26</t>
+          <t>830715-31-CM26</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -13522,22 +13522,22 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>60.511.139-4</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE PARINACOTA</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -13562,13 +13562,13 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>3299.93</v>
+        <v>8540.17</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>1774-32-CM26</t>
+          <t>720-97-CM26</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -13583,7 +13583,7 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -13593,12 +13593,12 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>60.804.001-3</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>ADMINISTRACIÓN ADUANA DE ARICA</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -13623,13 +13623,13 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>21726.85</v>
+        <v>73348.14999999999</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>1075963-4041-CM26</t>
+          <t>720-98-CM26</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -13644,22 +13644,22 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -13684,13 +13684,13 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>3264.15</v>
+        <v>18394.45</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>5702-204-CM26</t>
+          <t>5855-105-CM26</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -13700,27 +13700,27 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>69.251.000-3</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>Ilustre Municipalidad de Camarones</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -13745,13 +13745,13 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>5459.95</v>
+        <v>83211.14</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>1087-50-CM26</t>
+          <t>5855-106-CM26</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -13761,27 +13761,27 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.251.000-3</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>Ilustre Municipalidad de Camarones</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -13806,13 +13806,13 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>4301.54</v>
+        <v>77965.63</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>830715-31-CM26</t>
+          <t>1087-51-CM26</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -13822,27 +13822,27 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>60.511.139-4</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE PARINACOTA</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -13867,13 +13867,13 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>8540.17</v>
+        <v>2293.79</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>720-97-CM26</t>
+          <t>635-353-CM26</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -13883,12 +13883,12 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
@@ -13898,12 +13898,12 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.606.000-7</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -13928,13 +13928,13 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>73348.14999999999</v>
+        <v>32805.89</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>720-98-CM26</t>
+          <t>963423-62-CM26</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -13944,12 +13944,12 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
@@ -13959,12 +13959,12 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.980.850-9</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -13989,13 +13989,13 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>18394.45</v>
+        <v>3117.95</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>5855-105-CM26</t>
+          <t>1075963-4970-CM26</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -14010,7 +14010,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -14020,12 +14020,12 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>69.251.000-3</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>I.Municipalidad de Camarones</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -14050,13 +14050,13 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>83211.14</v>
+        <v>5350.82</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>5855-106-CM26</t>
+          <t>5611-34-CM26</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -14071,22 +14071,22 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>69.251.000-3</t>
+          <t>61.813.000-2</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>I.Municipalidad de Camarones</t>
+          <t>SERVICIO REGIONAL DE LA VIVIENDA Y URBAN</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -14111,13 +14111,13 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>77965.63</v>
+        <v>6671.19</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>1087-51-CM26</t>
+          <t>1087-68-CM26</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -14132,7 +14132,7 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
@@ -14172,13 +14172,13 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>2293.79</v>
+        <v>3382.3</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>635-353-CM26</t>
+          <t>1075963-5216-CM26</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -14193,7 +14193,7 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
@@ -14203,12 +14203,12 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>61.606.000-7</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -14233,13 +14233,13 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>32805.89</v>
+        <v>9146.93</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>963423-62-CM26</t>
+          <t>2366-250-CM26</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -14254,7 +14254,7 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
@@ -14264,12 +14264,12 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>61.980.850-9</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Zona de Bienestar Arica</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -14294,13 +14294,13 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>3117.95</v>
+        <v>32392.28</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>1075963-4970-CM26</t>
+          <t>2585-267-CM26</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -14315,22 +14315,22 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -14355,13 +14355,13 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>5350.82</v>
+        <v>22695.81</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>5611-34-CM26</t>
+          <t>5702-283-CM26</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -14376,7 +14376,7 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
@@ -14386,12 +14386,12 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>61.813.000-2</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>SERVICIO REGIONAL DE LA VIVIENDA Y URBAN</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -14416,13 +14416,13 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>6671.19</v>
+        <v>2921.78</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>1087-68-CM26</t>
+          <t>830715-33-CM26</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -14437,22 +14437,22 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>60.511.139-4</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE PARINACOTA</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -14477,13 +14477,13 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>3382.3</v>
+        <v>9316.59</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>1075963-5216-CM26</t>
+          <t>1346279-44-CM26</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -14498,7 +14498,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
@@ -14508,12 +14508,12 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -14538,13 +14538,13 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>9146.93</v>
+        <v>4026.04</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>2021-74-CM26</t>
+          <t>5358-93-CM26</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -14559,22 +14559,22 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>61.101.040-0</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Estado Mayor Conjunto</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -14599,13 +14599,13 @@
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>10156.98</v>
+        <v>11048.74</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>2366-250-CM26</t>
+          <t>5622-10-CM26</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -14620,7 +14620,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
@@ -14630,12 +14630,12 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.979.000-6</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERV NACIONAL DE PESCA</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -14660,13 +14660,13 @@
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>32392.28</v>
+        <v>2343.67</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>2585-267-CM26</t>
+          <t>4022-244-CM26</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -14676,27 +14676,27 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>69.250.800-9</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PUTRE</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -14721,13 +14721,13 @@
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>22695.81</v>
+        <v>22400.68</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>5702-283-CM26</t>
+          <t>1087-96-CM26</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -14737,12 +14737,12 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
@@ -14752,12 +14752,12 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -14782,13 +14782,13 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>2921.78</v>
+        <v>2693.68</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>830715-33-CM26</t>
+          <t>1443565-16-CM26</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -14798,12 +14798,12 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
@@ -14813,12 +14813,12 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>60.511.139-4</t>
+          <t>61.312.000-9</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE PARINACOTA</t>
+          <t>INIA</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -14843,13 +14843,13 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>9316.59</v>
+        <v>3011.41</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>1346279-44-CM26</t>
+          <t>720-103-CM26</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -14859,12 +14859,12 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
@@ -14874,12 +14874,12 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -14904,13 +14904,13 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>4026.04</v>
+        <v>77431.35000000001</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>5358-93-CM26</t>
+          <t>941739-38-CM26</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -14920,12 +14920,12 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
@@ -14935,7 +14935,7 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>70.770.800-K</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
@@ -14965,13 +14965,13 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>11048.74</v>
+        <v>19079.69</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>5622-10-CM26</t>
+          <t>1075963-6508-CM26</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -14981,27 +14981,27 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>61.979.000-6</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Pesca y Acuicultura</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -15026,13 +15026,13 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>2343.67</v>
+        <v>5303.03</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>1093870-3-CM26</t>
+          <t>5702-350-CM26</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -15042,12 +15042,12 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
@@ -15057,12 +15057,12 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>65.184.303-0</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE EDUCACION SUPERIOR</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -15087,13 +15087,13 @@
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>6653.66</v>
+        <v>2754.79</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>4022-244-CM26</t>
+          <t>635-642-CM26</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -15108,22 +15108,22 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>69.250.800-9</t>
+          <t>61.606.000-7</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Putre</t>
+          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -15148,13 +15148,13 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>22400.68</v>
+        <v>8941.84</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>1087-96-CM26</t>
+          <t>1087-115-CM26</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -15169,7 +15169,7 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
@@ -15209,13 +15209,13 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>2693.68</v>
+        <v>8794.24</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>720-103-CM26</t>
+          <t>5702-380-CM26</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -15225,12 +15225,12 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
@@ -15240,12 +15240,12 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -15270,13 +15270,13 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>77431.35000000001</v>
+        <v>2799.83</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>1443565-16-CM26</t>
+          <t>720-153-CM26</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -15286,27 +15286,27 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>61.312.000-9</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>INSTITUTO DE INVESTIGACIONES AGROPECUARIAS</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -15331,13 +15331,13 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>3011.41</v>
+        <v>62497.17</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>941739-38-CM26</t>
+          <t>1075963-7514-CM26</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -15347,12 +15347,12 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
@@ -15362,12 +15362,12 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>70.770.800-K</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -15392,13 +15392,13 @@
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>19079.69</v>
+        <v>6779.96</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>1075963-6508-CM26</t>
+          <t>696027-27-CM26</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -15408,12 +15408,12 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -15423,12 +15423,12 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -15453,13 +15453,13 @@
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>5303.03</v>
+        <v>4352.98</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>5702-350-CM26</t>
+          <t>5667-67-CM26</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -15469,27 +15469,27 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>61.979.080-4</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -15514,13 +15514,13 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>2754.79</v>
+        <v>2347.24</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>635-642-CM26</t>
+          <t>5702-428-CM26</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -15530,12 +15530,12 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
@@ -15545,12 +15545,12 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>61.606.000-7</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -15575,13 +15575,13 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>8941.84</v>
+        <v>2808.58</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>1087-115-CM26</t>
+          <t>5702-427-CM26</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -15591,12 +15591,12 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
@@ -15606,12 +15606,12 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -15636,13 +15636,13 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>8794.24</v>
+        <v>2808.58</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>5702-380-CM26</t>
+          <t>1087-130-CM26</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -15657,7 +15657,7 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
@@ -15667,12 +15667,12 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -15697,13 +15697,13 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>2799.83</v>
+        <v>2816.97</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>720-153-CM26</t>
+          <t>1337362-33-CM26</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -15718,7 +15718,7 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
@@ -15728,12 +15728,12 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -15758,13 +15758,13 @@
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>62497.17</v>
+        <v>2425.19</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>2021-111-CM26</t>
+          <t>720-165-CM26</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -15779,7 +15779,7 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
@@ -15789,12 +15789,12 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>61.101.040-0</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Estado Mayor Conjunto</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -15804,12 +15804,12 @@
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>EMPRESA NACIONAL DE ENERGIA ENEX S.A.</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
         <is>
-          <t>92.011.000-2</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K252" t="inlineStr"/>
@@ -15819,13 +15819,13 @@
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>6089.45</v>
+        <v>7321.46</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>1075963-7514-CM26</t>
+          <t>4022-333-CM26</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -15840,7 +15840,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
@@ -15850,12 +15850,12 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>69.250.800-9</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PUTRE</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -15880,13 +15880,13 @@
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>6779.96</v>
+        <v>22638.26</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>696027-27-CM26</t>
+          <t>509920-5-CM26</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -15901,7 +15901,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
@@ -15911,12 +15911,12 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -15941,13 +15941,13 @@
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>4352.98</v>
+        <v>2433.61</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>5667-67-CM26</t>
+          <t>5667-72-CM26</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -15962,12 +15962,12 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
@@ -15977,7 +15977,7 @@
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>SEREMI de Educación Arica y Parinacota</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -16002,13 +16002,13 @@
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>2347.24</v>
+        <v>2387.3</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>1087-130-CM26</t>
+          <t>1087-139-CM26</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -16023,7 +16023,7 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
@@ -16063,13 +16063,13 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>2816.97</v>
+        <v>3312.06</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>5702-427-CM26</t>
+          <t>1075963-8208-CM26</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -16084,22 +16084,22 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -16124,13 +16124,13 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>2808.58</v>
+        <v>4590.53</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>5702-428-CM26</t>
+          <t>2369-67-CM26</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -16145,7 +16145,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
@@ -16155,12 +16155,12 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -16170,28 +16170,32 @@
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
-        </is>
-      </c>
-      <c r="K258" t="inlineStr"/>
+          <t>79.588.870-5</t>
+        </is>
+      </c>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L258" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>2808.58</v>
+        <v>0</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>1337362-33-CM26</t>
+          <t>1774-74-CM26</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -16206,7 +16210,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
@@ -16216,12 +16220,12 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>60.804.001-3</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL DE ARICA Y PARINACOTA</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -16246,13 +16250,13 @@
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>2425.19</v>
+        <v>5044.46</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>720-165-CM26</t>
+          <t>696027-35-CM26</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -16267,22 +16271,22 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -16307,13 +16311,13 @@
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>7321.46</v>
+        <v>6658.05</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>4022-333-CM26</t>
+          <t>1075963-8659-CM26</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -16323,12 +16327,12 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
@@ -16338,12 +16342,12 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>69.250.800-9</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Putre</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -16368,13 +16372,13 @@
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>22638.26</v>
+        <v>5287.65</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>509920-5-CM26</t>
+          <t>1075963-8732-CM26</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -16384,27 +16388,27 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Servicio Nacional del Patrimonio Cultural</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -16429,13 +16433,13 @@
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>2433.61</v>
+        <v>7594.66</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>5667-72-CM26</t>
+          <t>720-155-CM26</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -16445,12 +16449,12 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
@@ -16460,12 +16464,12 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>61.979.080-4</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>SEREMI de Educación Arica y Parinacota</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -16490,13 +16494,13 @@
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>2387.3</v>
+        <v>7742.83</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>1087-139-CM26</t>
+          <t>2366-434-CM26</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -16506,12 +16510,12 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
@@ -16521,12 +16525,12 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -16551,13 +16555,13 @@
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>3312.06</v>
+        <v>34438.48</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>1075963-8208-CM26</t>
+          <t>5857-25-CM26</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -16567,12 +16571,12 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
@@ -16582,12 +16586,12 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>69.251.000-3</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>Ilustre Municipalidad de Camarones</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -16612,13 +16616,13 @@
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>4590.53</v>
+        <v>25361.43</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>696027-35-CM26</t>
+          <t>720-224-CM26</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -16628,27 +16632,27 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -16673,13 +16677,13 @@
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>6658.05</v>
+        <v>35793.31</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>2369-67-CM26</t>
+          <t>5702-506-CM26</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -16689,27 +16693,27 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -16719,32 +16723,28 @@
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J267" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
-        </is>
-      </c>
-      <c r="K267" t="inlineStr">
-        <is>
-          <t>Atacama</t>
-        </is>
-      </c>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K267" t="inlineStr"/>
       <c r="L267" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>0</v>
+        <v>2703.35</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>1774-74-CM26</t>
+          <t>1075963-9267-CM26</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -16754,27 +16754,27 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>60.804.001-3</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>ADMINISTRACIÓN ADUANA DE ARICA</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
@@ -16799,13 +16799,13 @@
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>5044.46</v>
+        <v>4715.72</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>1075963-8659-CM26</t>
+          <t>5702-526-CM26</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -16820,22 +16820,22 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -16860,13 +16860,13 @@
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>5287.65</v>
+        <v>4756.17</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>1075963-8732-CM26</t>
+          <t>4022-381-CM26</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -16881,22 +16881,22 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>69.250.800-9</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PUTRE</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -16921,13 +16921,13 @@
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>7594.66</v>
+        <v>21233</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>720-155-CM26</t>
+          <t>1087-177-CM26</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -16937,12 +16937,12 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
@@ -16952,12 +16952,12 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
@@ -16982,13 +16982,13 @@
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>7742.83</v>
+        <v>6318.51</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>2366-434-CM26</t>
+          <t>1084148-71-CM26</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -16998,12 +16998,12 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
@@ -17013,12 +17013,12 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -17043,13 +17043,13 @@
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>34438.48</v>
+        <v>3290.3</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>5857-25-CM26</t>
+          <t>1075963-10575-CM26</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -17059,12 +17059,12 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
@@ -17074,12 +17074,12 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>69.251.000-3</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>I.Municipalidad de Camarones</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -17104,13 +17104,13 @@
         </is>
       </c>
       <c r="M273" s="2" t="n">
-        <v>25361.43</v>
+        <v>4893.09</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>720-224-CM26</t>
+          <t>1075963-10724-CM26</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -17120,27 +17120,27 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -17165,13 +17165,13 @@
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>35793.31</v>
+        <v>4886.93</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>5702-506-CM26</t>
+          <t>720-258-CM26</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -17181,12 +17181,12 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
@@ -17196,12 +17196,12 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -17226,13 +17226,13 @@
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>2703.35</v>
+        <v>4188.8</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>1075963-9267-CM26</t>
+          <t>5360-204-CM26</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -17242,12 +17242,12 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
@@ -17257,12 +17257,12 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -17287,13 +17287,13 @@
         </is>
       </c>
       <c r="M276" s="2" t="n">
-        <v>4715.72</v>
+        <v>6279.05</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>5702-526-CM26</t>
+          <t>1075963-10879-CM26</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -17303,27 +17303,27 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -17348,13 +17348,13 @@
         </is>
       </c>
       <c r="M277" s="2" t="n">
-        <v>4756.17</v>
+        <v>4849.17</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>4022-381-CM26</t>
+          <t>1232837-198-CM26</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -17364,12 +17364,12 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
@@ -17379,12 +17379,12 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>69.250.800-9</t>
+          <t>65.166.511-6</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Putre</t>
+          <t>CORPORACION MUNICIPAL DE FOMENTO   PRODUCTIVO DE ARICA</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
@@ -17409,13 +17409,13 @@
         </is>
       </c>
       <c r="M278" s="2" t="n">
-        <v>21233</v>
+        <v>2336.3</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>1087-177-CM26</t>
+          <t>5611-75-CM26</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -17430,7 +17430,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
@@ -17440,12 +17440,12 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.813.000-2</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>SERVICIO REGIONAL DE LA VIVIENDA Y URBAN</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -17470,13 +17470,13 @@
         </is>
       </c>
       <c r="M279" s="2" t="n">
-        <v>6318.51</v>
+        <v>6532.96</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>1084148-71-CM26</t>
+          <t>1443565-42-CM26</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -17491,22 +17491,22 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>61.312.000-9</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>INIA</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -17531,13 +17531,13 @@
         </is>
       </c>
       <c r="M280" s="2" t="n">
-        <v>3290.3</v>
+        <v>9533.76</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>1075963-10575-CM26</t>
+          <t>5702-616-CM26</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -17552,22 +17552,22 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
@@ -17592,13 +17592,13 @@
         </is>
       </c>
       <c r="M281" s="2" t="n">
-        <v>4893.09</v>
+        <v>4899.72</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>720-258-CM26</t>
+          <t>5649-35-CM26</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -17613,7 +17613,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
@@ -17623,12 +17623,12 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.979.030-8</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -17653,13 +17653,13 @@
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>4188.8</v>
+        <v>2323.7</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>1075963-10724-CM26</t>
+          <t>5358-215-CM26</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -17674,7 +17674,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
@@ -17684,12 +17684,12 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
@@ -17714,13 +17714,13 @@
         </is>
       </c>
       <c r="M283" s="2" t="n">
-        <v>4886.93</v>
+        <v>11838.4</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>5360-204-CM26</t>
+          <t>1087-197-CM26</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -17730,27 +17730,27 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -17775,13 +17775,13 @@
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>6279.05</v>
+        <v>2321.22</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>1075963-10879-CM26</t>
+          <t>830715-66-CM26</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -17791,12 +17791,12 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
@@ -17806,12 +17806,12 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>60.511.139-4</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE PARINACOTA</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -17836,13 +17836,13 @@
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>4849.17</v>
+        <v>8228.129999999999</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>1232837-198-CM26</t>
+          <t>830715-68-CM26</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -17852,12 +17852,12 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
@@ -17867,12 +17867,12 @@
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>65.166.511-6</t>
+          <t>60.511.139-4</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE FOMENTO   PRODUCTIVO DE ARICA</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE PARINACOTA</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
@@ -17897,13 +17897,13 @@
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>2336.3</v>
+        <v>15333.11</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>1443565-42-CM26</t>
+          <t>635-1302-CM26</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -17913,12 +17913,12 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
@@ -17928,12 +17928,12 @@
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>61.312.000-9</t>
+          <t>61.606.000-7</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>INIA</t>
+          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
@@ -17958,13 +17958,13 @@
         </is>
       </c>
       <c r="M287" s="2" t="n">
-        <v>9533.76</v>
+        <v>2296.27</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>5611-75-CM26</t>
+          <t>4022-468-CM26</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -17974,27 +17974,27 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>61.813.000-2</t>
+          <t>69.250.800-9</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>SERVICIO REGIONAL DE LA VIVIENDA Y URBAN</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PUTRE</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
@@ -18019,13 +18019,13 @@
         </is>
       </c>
       <c r="M288" s="2" t="n">
-        <v>6532.96</v>
+        <v>21340.85</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>5702-616-CM26</t>
+          <t>830715-70-CM26</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -18035,27 +18035,27 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>60.511.139-4</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE PARINACOTA</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
@@ -18080,13 +18080,13 @@
         </is>
       </c>
       <c r="M289" s="2" t="n">
-        <v>4899.72</v>
+        <v>15302.97</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>5649-35-CM26</t>
+          <t>830715-71-CM26</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -18096,27 +18096,27 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>61.979.030-8</t>
+          <t>60.511.139-4</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>MINISTERIO DE BIENES NACIONALES</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE PARINACOTA</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
@@ -18141,13 +18141,13 @@
         </is>
       </c>
       <c r="M290" s="2" t="n">
-        <v>2323.7</v>
+        <v>14869.35</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>5358-215-CM26</t>
+          <t>720-289-CM26</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -18157,27 +18157,27 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -18202,7 +18202,434 @@
         </is>
       </c>
       <c r="M291" s="2" t="n">
-        <v>11838.4</v>
+        <v>72948.71000000001</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>5602-272-CM26</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>61.601.000-K</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+        </is>
+      </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J292" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K292" t="inlineStr"/>
+      <c r="L292" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M292" s="2" t="n">
+        <v>3752.38</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>1075963-12645-CM26</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>61.606.001-5</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+        </is>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J293" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K293" t="inlineStr"/>
+      <c r="L293" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M293" s="2" t="n">
+        <v>7486.85</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>5855-299-CM26</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>69.251.000-3</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>Ilustre Municipalidad de Camarones</t>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J294" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K294" t="inlineStr"/>
+      <c r="L294" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M294" s="2" t="n">
+        <v>44936.58</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>1087-206-CM26</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>61.313.000-4</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>CORP NACIONAL FORESTAL</t>
+        </is>
+      </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J295" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K295" t="inlineStr"/>
+      <c r="L295" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M295" s="2" t="n">
+        <v>3091.32</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>830715-74-CM26</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>60.511.139-4</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE PARINACOTA</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J296" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K296" t="inlineStr"/>
+      <c r="L296" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M296" s="2" t="n">
+        <v>14648.72</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>5702-701-CM26</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>61.979.020-0</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+        </is>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J297" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K297" t="inlineStr"/>
+      <c r="L297" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M297" s="2" t="n">
+        <v>2266.97</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>1110404-963-CM26</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>62.000.660-2</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J298" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K298" t="inlineStr"/>
+      <c r="L298" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M298" s="2" t="n">
+        <v>73882.49000000001</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/suministro-de-combustibles/arica-y-parinacota.xlsx
+++ b/docs/oc-regiones/suministro-de-combustibles/arica-y-parinacota.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M299"/>
+  <dimension ref="A1:M307"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4544,7 +4544,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>720-213-CM25</t>
+          <t>720-212-CM25</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4603,13 +4603,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>65873.77</v>
+        <v>4781.13</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>720-212-CM25</t>
+          <t>1774-78-CM25</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>60.804.001-3</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>4781.13</v>
+        <v>11899.7</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1774-78-CM25</t>
+          <t>720-213-CM25</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4699,12 +4699,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>60.804.001-3</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE ADUANAS</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>11899.7</v>
+        <v>65873.77</v>
       </c>
     </row>
     <row r="67">
@@ -6299,7 +6299,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>5702-509-CM25</t>
+          <t>1346279-122-CM25</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -6324,12 +6324,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -6364,7 +6364,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>1346279-122-CM25</t>
+          <t>5702-509-CM25</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6389,12 +6389,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -7014,7 +7014,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>5952-239-CM25</t>
+          <t>720-352-CM25</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -7034,17 +7034,17 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -7073,13 +7073,13 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>4124.77</v>
+        <v>70121.09</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>720-352-CM25</t>
+          <t>5952-239-CM25</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -7099,17 +7099,17 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -7138,7 +7138,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>70121.09</v>
+        <v>4124.77</v>
       </c>
     </row>
     <row r="104">
@@ -7404,7 +7404,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>5611-94-CM25</t>
+          <t>1075963-23723-CM25</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -7424,17 +7424,17 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>61.813.000-2</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>SERVICIO REGIONAL DE LA VIVIENDA Y URBAN</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -7463,13 +7463,13 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>2119</v>
+        <v>4926.53</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>1075963-23723-CM25</t>
+          <t>5611-94-CM25</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7489,17 +7489,17 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>61.813.000-2</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>SERVICIO REGIONAL DE LA VIVIENDA Y URBAN</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -7528,7 +7528,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>4926.53</v>
+        <v>2119</v>
       </c>
     </row>
     <row r="110">
@@ -7924,7 +7924,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>5687-42-CM25</t>
+          <t>830715-62-CM25</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7949,12 +7949,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>61.978.920-2</t>
+          <t>60.511.139-4</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE PARINACOTA</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7983,13 +7983,13 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>2687.39</v>
+        <v>5775.83</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>830715-62-CM25</t>
+          <t>5687-42-CM25</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -8014,12 +8014,12 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>60.511.139-4</t>
+          <t>61.978.920-2</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE PARINACOTA</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -8048,13 +8048,13 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>5775.83</v>
+        <v>2687.39</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>5358-309-CM25</t>
+          <t>963423-2640-CM25</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -8079,12 +8079,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>61.980.850-9</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -8113,13 +8113,13 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>2581.71</v>
+        <v>2168.64</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>963423-2640-CM25</t>
+          <t>5358-309-CM25</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>61.980.850-9</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -8178,7 +8178,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>2168.64</v>
+        <v>2581.71</v>
       </c>
     </row>
     <row r="120">
@@ -8444,7 +8444,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>5702-716-CM25</t>
+          <t>5702-715-CM25</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -8509,7 +8509,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>5702-715-CM25</t>
+          <t>5702-716-CM25</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -9484,7 +9484,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>5857-55-CM25</t>
+          <t>5855-274-CM25</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -9543,13 +9543,13 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>12573.74</v>
+        <v>31434.35</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>5855-274-CM25</t>
+          <t>5857-55-CM25</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -9608,13 +9608,13 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>31434.35</v>
+        <v>12573.74</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>5855-275-CM25</t>
+          <t>5649-27-CM25</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -9634,17 +9634,17 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>69.251.000-3</t>
+          <t>61.979.030-8</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Camarones</t>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -9673,13 +9673,13 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>31326.36</v>
+        <v>2245.06</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>5649-27-CM25</t>
+          <t>1346279-190-CM25</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -9699,17 +9699,17 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>61.979.030-8</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>MINISTERIO DE BIENES NACIONALES</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -9738,13 +9738,13 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>2245.06</v>
+        <v>2192.85</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>1346279-190-CM25</t>
+          <t>5855-275-CM25</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -9769,12 +9769,12 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>69.251.000-3</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>Ilustre Municipalidad de Camarones</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -9803,7 +9803,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>2192.85</v>
+        <v>31326.36</v>
       </c>
     </row>
     <row r="145">
@@ -9939,7 +9939,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>720-489-CM25</t>
+          <t>1075963-49124-CM25</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -9959,17 +9959,17 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -9998,13 +9998,13 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>2206.39</v>
+        <v>4425.39</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>1075963-49124-CM25</t>
+          <t>720-489-CM25</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -10024,17 +10024,17 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -10063,13 +10063,13 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>4425.39</v>
+        <v>2206.39</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>720-496-CM25</t>
+          <t>5622-34-CM25</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -10094,12 +10094,12 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.979.000-6</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>SERV NACIONAL DE PESCA</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -10128,13 +10128,13 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>73269.92999999999</v>
+        <v>2198.1</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>5792-23-CM25</t>
+          <t>720-496-CM25</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -10159,12 +10159,12 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>61.702.000-9</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE GEOLOGIA Y MINERIA</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -10193,13 +10193,13 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>2644.55</v>
+        <v>73269.92999999999</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>5622-34-CM25</t>
+          <t>5792-23-CM25</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -10224,12 +10224,12 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>61.979.000-6</t>
+          <t>61.702.000-9</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>SERV NACIONAL DE PESCA</t>
+          <t>SERVICIO NACIONAL DE GEOLOGIA Y MINERIA</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -10258,7 +10258,7 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>2198.1</v>
+        <v>2644.55</v>
       </c>
     </row>
     <row r="152">
@@ -10394,7 +10394,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>5420-296-CM25</t>
+          <t>5420-295-CM25</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -10453,13 +10453,13 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>4252.74</v>
+        <v>6379.11</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>5420-295-CM25</t>
+          <t>5420-296-CM25</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -10518,7 +10518,7 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>6379.11</v>
+        <v>4252.74</v>
       </c>
     </row>
     <row r="156">
@@ -11174,7 +11174,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>1774-236-CM25</t>
+          <t>5702-916-CM25</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -11199,12 +11199,12 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>60.804.001-3</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE ADUANAS</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -11233,7 +11233,7 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>4089.8</v>
+        <v>2690.66</v>
       </c>
     </row>
     <row r="167">
@@ -11304,7 +11304,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>5702-916-CM25</t>
+          <t>1774-236-CM25</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -11329,12 +11329,12 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>60.804.001-3</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -11363,7 +11363,7 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>2690.66</v>
+        <v>4089.8</v>
       </c>
     </row>
     <row r="169">
@@ -11629,7 +11629,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2202-1094-CM25</t>
+          <t>720-1126-CM25</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -11654,12 +11654,12 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>61.602.241-5</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ARAUCANIA NORTE HOSPITAL CURACAUTIN</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -11688,13 +11688,13 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>4356.59</v>
+        <v>8713.17</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>720-1126-CM25</t>
+          <t>2202-1094-CM25</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -11719,12 +11719,12 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.602.241-5</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>SERVICIO SALUD ARAUCANIA NORTE HOSPITAL CURACAUTIN</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -11753,7 +11753,7 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>8713.17</v>
+        <v>4356.59</v>
       </c>
     </row>
     <row r="175">
@@ -12214,7 +12214,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>5702-978-CM25</t>
+          <t>1110404-1633-CM25</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -12239,12 +12239,12 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -12273,13 +12273,13 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>3316.6</v>
+        <v>2321.62</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>1110404-1633-CM25</t>
+          <t>5702-978-CM25</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -12304,12 +12304,12 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -12338,7 +12338,7 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>2321.62</v>
+        <v>3316.6</v>
       </c>
     </row>
     <row r="184">
@@ -12994,7 +12994,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>720-10-CM26</t>
+          <t>720-12-CM26</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -13053,7 +13053,7 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>5793.25</v>
+        <v>3013.06</v>
       </c>
     </row>
     <row r="195">
@@ -13124,7 +13124,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>720-12-CM26</t>
+          <t>720-10-CM26</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -13183,7 +13183,7 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>3013.06</v>
+        <v>5793.25</v>
       </c>
     </row>
     <row r="197">
@@ -13709,7 +13709,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>5855-77-CM26</t>
+          <t>3527-42-CM26</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -13729,17 +13729,17 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>69.251.000-3</t>
+          <t>61.101.037-0</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Camarones</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -13768,13 +13768,13 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>16757.16</v>
+        <v>2457.72</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>3527-42-CM26</t>
+          <t>5855-77-CM26</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -13794,17 +13794,17 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>61.101.037-0</t>
+          <t>69.251.000-3</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>Ilustre Municipalidad de Camarones</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -13833,7 +13833,7 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>2457.72</v>
+        <v>16757.16</v>
       </c>
     </row>
     <row r="207">
@@ -14424,7 +14424,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>830715-31-CM26</t>
+          <t>720-97-CM26</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -14444,17 +14444,17 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>60.511.139-4</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE PARINACOTA</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -14483,13 +14483,13 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>8540.17</v>
+        <v>73348.14999999999</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>720-97-CM26</t>
+          <t>720-98-CM26</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -14548,13 +14548,13 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>73348.14999999999</v>
+        <v>18394.45</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>720-98-CM26</t>
+          <t>830715-31-CM26</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -14574,17 +14574,17 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>60.511.139-4</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE PARINACOTA</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -14613,7 +14613,7 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>18394.45</v>
+        <v>8540.17</v>
       </c>
     </row>
     <row r="219">
@@ -15529,7 +15529,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>5358-93-CM26</t>
+          <t>5622-10-CM26</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -15549,17 +15549,17 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>61.979.000-6</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>SERV NACIONAL DE PESCA</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -15588,13 +15588,13 @@
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>11048.74</v>
+        <v>2343.67</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>5622-10-CM26</t>
+          <t>5358-93-CM26</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -15614,17 +15614,17 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>61.979.000-6</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>SERV NACIONAL DE PESCA</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -15653,7 +15653,7 @@
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>2343.67</v>
+        <v>11048.74</v>
       </c>
     </row>
     <row r="235">
@@ -16569,7 +16569,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>5702-428-CM26</t>
+          <t>1087-130-CM26</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -16594,12 +16594,12 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -16628,13 +16628,13 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>2808.58</v>
+        <v>2816.97</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>1087-130-CM26</t>
+          <t>5702-428-CM26</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -16659,12 +16659,12 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -16693,7 +16693,7 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>2816.97</v>
+        <v>2808.58</v>
       </c>
     </row>
     <row r="251">
@@ -16829,7 +16829,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>720-165-CM26</t>
+          <t>509920-5-CM26</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -16849,17 +16849,17 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -16888,7 +16888,7 @@
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>7321.46</v>
+        <v>2433.61</v>
       </c>
     </row>
     <row r="254">
@@ -16959,7 +16959,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>509920-5-CM26</t>
+          <t>720-165-CM26</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -16979,17 +16979,17 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -17018,7 +17018,7 @@
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>2433.61</v>
+        <v>7321.46</v>
       </c>
     </row>
     <row r="256">
@@ -18259,7 +18259,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>720-258-CM26</t>
+          <t>1075963-10724-CM26</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -18279,17 +18279,17 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -18318,13 +18318,13 @@
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>4188.8</v>
+        <v>4886.93</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>1075963-10724-CM26</t>
+          <t>720-258-CM26</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -18344,17 +18344,17 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -18383,7 +18383,7 @@
         </is>
       </c>
       <c r="M276" s="2" t="n">
-        <v>4886.93</v>
+        <v>4188.8</v>
       </c>
     </row>
     <row r="277">
@@ -18454,7 +18454,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>1075963-10879-CM26</t>
+          <t>1232837-198-CM26</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -18479,12 +18479,12 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>65.166.511-6</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>CORPORACION MUNICIPAL DE FOMENTO   PRODUCTIVO DE ARICA</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
@@ -18513,13 +18513,13 @@
         </is>
       </c>
       <c r="M278" s="2" t="n">
-        <v>4849.17</v>
+        <v>2336.3</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>1232837-198-CM26</t>
+          <t>1075963-10879-CM26</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -18544,12 +18544,12 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>65.166.511-6</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE FOMENTO   PRODUCTIVO DE ARICA</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -18578,13 +18578,13 @@
         </is>
       </c>
       <c r="M279" s="2" t="n">
-        <v>2336.3</v>
+        <v>4849.17</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>5611-75-CM26</t>
+          <t>1443565-42-CM26</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -18604,17 +18604,17 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>61.813.000-2</t>
+          <t>61.312.000-9</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>SERVICIO REGIONAL DE LA VIVIENDA Y URBAN</t>
+          <t>INIA</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -18643,13 +18643,13 @@
         </is>
       </c>
       <c r="M280" s="2" t="n">
-        <v>6532.96</v>
+        <v>9533.76</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>1443565-42-CM26</t>
+          <t>5702-616-CM26</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -18669,17 +18669,17 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>61.312.000-9</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>INIA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
@@ -18708,13 +18708,13 @@
         </is>
       </c>
       <c r="M281" s="2" t="n">
-        <v>9533.76</v>
+        <v>4899.72</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>5702-616-CM26</t>
+          <t>5611-75-CM26</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -18739,12 +18739,12 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>61.813.000-2</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO REGIONAL DE LA VIVIENDA Y URBAN</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -18773,7 +18773,7 @@
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>4899.72</v>
+        <v>6532.96</v>
       </c>
     </row>
     <row r="283">
@@ -18909,7 +18909,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>1087-197-CM26</t>
+          <t>1075963-11564-CM26</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -18924,22 +18924,22 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -18968,13 +18968,13 @@
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>2321.22</v>
+        <v>5128.59</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>830715-66-CM26</t>
+          <t>1087-197-CM26</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -18989,22 +18989,22 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>60.511.139-4</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE PARINACOTA</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
@@ -19033,7 +19033,7 @@
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>8228.129999999999</v>
+        <v>2321.22</v>
       </c>
     </row>
     <row r="287">
@@ -19104,7 +19104,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>4022-468-CM26</t>
+          <t>830715-66-CM26</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -19119,7 +19119,7 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
@@ -19129,12 +19129,12 @@
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>69.250.800-9</t>
+          <t>60.511.139-4</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE PUTRE</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE PARINACOTA</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
@@ -19163,7 +19163,7 @@
         </is>
       </c>
       <c r="M288" s="2" t="n">
-        <v>21340.85</v>
+        <v>8228.129999999999</v>
       </c>
     </row>
     <row r="289">
@@ -19234,7 +19234,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>830715-70-CM26</t>
+          <t>4022-468-CM26</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -19249,7 +19249,7 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
@@ -19259,12 +19259,12 @@
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>60.511.139-4</t>
+          <t>69.250.800-9</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE PARINACOTA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PUTRE</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
@@ -19293,13 +19293,13 @@
         </is>
       </c>
       <c r="M290" s="2" t="n">
-        <v>15302.97</v>
+        <v>21340.85</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>830715-71-CM26</t>
+          <t>830715-70-CM26</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -19314,7 +19314,7 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
@@ -19358,13 +19358,13 @@
         </is>
       </c>
       <c r="M291" s="2" t="n">
-        <v>14869.35</v>
+        <v>15302.97</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>720-289-CM26</t>
+          <t>830715-71-CM26</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -19379,22 +19379,22 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>60.511.139-4</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE PARINACOTA</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
@@ -19423,13 +19423,13 @@
         </is>
       </c>
       <c r="M292" s="2" t="n">
-        <v>72948.71000000001</v>
+        <v>14869.35</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>5602-272-CM26</t>
+          <t>720-289-CM26</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -19444,7 +19444,7 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
@@ -19454,12 +19454,12 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
@@ -19488,13 +19488,13 @@
         </is>
       </c>
       <c r="M293" s="2" t="n">
-        <v>3752.38</v>
+        <v>72948.71000000001</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>5855-299-CM26</t>
+          <t>5602-272-CM26</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -19509,22 +19509,22 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>69.251.000-3</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Camarones</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
@@ -19553,13 +19553,13 @@
         </is>
       </c>
       <c r="M294" s="2" t="n">
-        <v>44936.58</v>
+        <v>3752.38</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>1075963-12645-CM26</t>
+          <t>5855-299-CM26</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -19584,12 +19584,12 @@
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>69.251.000-3</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>Ilustre Municipalidad de Camarones</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
@@ -19618,13 +19618,13 @@
         </is>
       </c>
       <c r="M295" s="2" t="n">
-        <v>7486.85</v>
+        <v>44936.58</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>830715-74-CM26</t>
+          <t>1075963-12645-CM26</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -19639,22 +19639,22 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>60.511.139-4</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE PARINACOTA</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
@@ -19683,13 +19683,13 @@
         </is>
       </c>
       <c r="M296" s="2" t="n">
-        <v>14648.72</v>
+        <v>7486.85</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>5702-701-CM26</t>
+          <t>830715-74-CM26</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -19709,17 +19709,17 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>60.511.139-4</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE PARINACOTA</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
@@ -19748,7 +19748,7 @@
         </is>
       </c>
       <c r="M297" s="2" t="n">
-        <v>2266.97</v>
+        <v>14648.72</v>
       </c>
     </row>
     <row r="298">
@@ -19879,6 +19879,526 @@
       </c>
       <c r="M299" s="2" t="n">
         <v>73882.49000000001</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>5702-701-CM26</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>61.979.020-0</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+        </is>
+      </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I300" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J300" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L300" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M300" s="2" t="n">
+        <v>2266.97</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>1087-209-CM26</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>61.313.000-4</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>CORP NACIONAL FORESTAL</t>
+        </is>
+      </c>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I301" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J301" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L301" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M301" s="2" t="n">
+        <v>8461.74</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>707409-99-CM26</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>70.574.900-0</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+        </is>
+      </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I302" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J302" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L302" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M302" s="2" t="n">
+        <v>6098.55</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>1075963-13004-CM26</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>61.606.001-5</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+        </is>
+      </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I303" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J303" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L303" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M303" s="2" t="n">
+        <v>4788.95</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>1489-28-CM26</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>61.979.110-k</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
+        </is>
+      </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I304" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J304" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L304" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M304" s="2" t="n">
+        <v>2288.78</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>1346279-126-CM26</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>62.000.970-9</t>
+        </is>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+        </is>
+      </c>
+      <c r="H305" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I305" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J305" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L305" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M305" s="2" t="n">
+        <v>2205.56</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>5702-768-CM26</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>61.979.020-0</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+        </is>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I306" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J306" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L306" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M306" s="2" t="n">
+        <v>6909.94</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>1075963-14089-CM26</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>61.606.001-5</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+        </is>
+      </c>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I307" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J307" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L307" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M307" s="2" t="n">
+        <v>5014.29</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/suministro-de-combustibles/arica-y-parinacota.xlsx
+++ b/docs/oc-regiones/suministro-de-combustibles/arica-y-parinacota.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M307"/>
+  <dimension ref="A1:M315"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -674,7 +674,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -2659,7 +2659,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1075963-15057-CM25</t>
+          <t>720-95-CM25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2679,17 +2679,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2718,13 +2718,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>3372.69</v>
+        <v>71261.42999999999</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>720-95-CM25</t>
+          <t>1075963-15057-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2744,17 +2744,17 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2783,7 +2783,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>71261.42999999999</v>
+        <v>3372.69</v>
       </c>
     </row>
     <row r="37">
@@ -2854,7 +2854,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>5855-73-CM25</t>
+          <t>1058823-4-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2879,12 +2879,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>69.251.000-3</t>
+          <t>60.318.000-3</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Camarones</t>
+          <t>CORP DE ASISTENCIA JUDICIAL DE LAS REG T</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2894,17 +2894,17 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2913,13 +2913,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>10794.36</v>
+        <v>5397.18</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1058823-4-CM25</t>
+          <t>5855-73-CM25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2944,12 +2944,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>60.318.000-3</t>
+          <t>69.251.000-3</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>CORP DE ASISTENCIA JUDICIAL DE LAS REG T</t>
+          <t>Ilustre Municipalidad de Camarones</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2959,17 +2959,17 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -2978,7 +2978,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>5397.18</v>
+        <v>10794.36</v>
       </c>
     </row>
     <row r="40">
@@ -3114,7 +3114,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>635-3194-CM25</t>
+          <t>3348-34-CM25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3139,12 +3139,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>61.606.000-7</t>
+          <t>61.101.082-6</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3173,13 +3173,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>2308.33</v>
+        <v>2413.25</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>3348-34-CM25</t>
+          <t>635-3194-CM25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>61.101.082-6</t>
+          <t>61.606.000-7</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3238,7 +3238,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>2413.25</v>
+        <v>2308.33</v>
       </c>
     </row>
     <row r="44">
@@ -3829,7 +3829,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1075963-19201-CM25</t>
+          <t>720-143-CM25</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3888,13 +3888,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>5482.43</v>
+        <v>33065.26</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>720-143-CM25</t>
+          <t>1075963-19201-CM25</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3919,12 +3919,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>33065.26</v>
+        <v>5482.43</v>
       </c>
     </row>
     <row r="55">
@@ -4024,7 +4024,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1084148-70-CM25</t>
+          <t>4022-278-CM25</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4044,17 +4044,17 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>69.250.800-9</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PUTRE</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -4083,13 +4083,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>2233.61</v>
+        <v>21272.52</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>3527-122-CM25</t>
+          <t>830715-33-CM25</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4109,17 +4109,17 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>61.101.037-0</t>
+          <t>60.511.139-4</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE PARINACOTA</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -4148,13 +4148,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>4148.14</v>
+        <v>5766.45</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>4022-278-CM25</t>
+          <t>1084148-70-CM25</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4174,17 +4174,17 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>69.250.800-9</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE PUTRE</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4213,13 +4213,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>21272.52</v>
+        <v>2233.61</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>830715-33-CM25</t>
+          <t>3527-122-CM25</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4239,17 +4239,17 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>60.511.139-4</t>
+          <t>61.101.037-0</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE PARINACOTA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4278,7 +4278,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>5766.45</v>
+        <v>4148.14</v>
       </c>
     </row>
     <row r="60">
@@ -4479,7 +4479,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>720-210-CM25</t>
+          <t>720-212-CM25</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4538,13 +4538,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>10093.5</v>
+        <v>4781.13</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>720-212-CM25</t>
+          <t>720-210-CM25</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4603,7 +4603,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>4781.13</v>
+        <v>10093.5</v>
       </c>
     </row>
     <row r="65">
@@ -4869,7 +4869,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2585-3560-CM25</t>
+          <t>1110404-471-CM25</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4928,13 +4928,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>72473.03999999999</v>
+        <v>70341.48</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>5358-155-CM25</t>
+          <t>838099-49-CM25</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4959,12 +4959,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>73.923.800-5</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4993,13 +4993,13 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>4902.59</v>
+        <v>6394.68</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1110404-471-CM25</t>
+          <t>2585-3560-CM25</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5024,12 +5024,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -5058,13 +5058,13 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>70341.48</v>
+        <v>72473.03999999999</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>838099-49-CM25</t>
+          <t>5358-155-CM25</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5089,12 +5089,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>73.923.800-5</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -5123,7 +5123,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>6394.68</v>
+        <v>4902.59</v>
       </c>
     </row>
     <row r="73">
@@ -6819,7 +6819,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>963423-2609-CM25</t>
+          <t>1572-266-CM25</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6844,12 +6844,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>61.980.850-9</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6878,7 +6878,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>2192.48</v>
+        <v>2505.69</v>
       </c>
     </row>
     <row r="100">
@@ -6949,7 +6949,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>1572-266-CM25</t>
+          <t>963423-2609-CM25</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6974,12 +6974,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.980.850-9</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -7008,7 +7008,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>2505.69</v>
+        <v>2192.48</v>
       </c>
     </row>
     <row r="102">
@@ -7404,7 +7404,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>1075963-23723-CM25</t>
+          <t>5611-94-CM25</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -7424,17 +7424,17 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>61.813.000-2</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>SERVICIO REGIONAL DE LA VIVIENDA Y URBAN</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -7463,13 +7463,13 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>4926.53</v>
+        <v>2119</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>5611-94-CM25</t>
+          <t>1075963-23723-CM25</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7489,17 +7489,17 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>61.813.000-2</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>SERVICIO REGIONAL DE LA VIVIENDA Y URBAN</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -7528,7 +7528,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>2119</v>
+        <v>4926.53</v>
       </c>
     </row>
     <row r="110">
@@ -8054,7 +8054,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>963423-2640-CM25</t>
+          <t>5358-309-CM25</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -8079,12 +8079,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>61.980.850-9</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -8113,13 +8113,13 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>2168.64</v>
+        <v>2581.71</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>5358-309-CM25</t>
+          <t>963423-2640-CM25</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>61.980.850-9</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -8178,7 +8178,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>2581.71</v>
+        <v>2168.64</v>
       </c>
     </row>
     <row r="120">
@@ -9484,7 +9484,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>5855-274-CM25</t>
+          <t>5857-55-CM25</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -9543,13 +9543,13 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>31434.35</v>
+        <v>12573.74</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>5857-55-CM25</t>
+          <t>5855-274-CM25</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -9608,13 +9608,13 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>12573.74</v>
+        <v>31434.35</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>5649-27-CM25</t>
+          <t>5855-275-CM25</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -9634,17 +9634,17 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>61.979.030-8</t>
+          <t>69.251.000-3</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>MINISTERIO DE BIENES NACIONALES</t>
+          <t>Ilustre Municipalidad de Camarones</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -9673,7 +9673,7 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>2245.06</v>
+        <v>31326.36</v>
       </c>
     </row>
     <row r="143">
@@ -9744,7 +9744,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>5855-275-CM25</t>
+          <t>5649-27-CM25</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -9764,17 +9764,17 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>69.251.000-3</t>
+          <t>61.979.030-8</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Camarones</t>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -9803,7 +9803,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>31326.36</v>
+        <v>2245.06</v>
       </c>
     </row>
     <row r="145">
@@ -10069,7 +10069,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>5622-34-CM25</t>
+          <t>720-496-CM25</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -10094,12 +10094,12 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>61.979.000-6</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>SERV NACIONAL DE PESCA</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -10128,13 +10128,13 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>2198.1</v>
+        <v>73269.92999999999</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>720-496-CM25</t>
+          <t>5792-23-CM25</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -10159,12 +10159,12 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.702.000-9</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>SERVICIO NACIONAL DE GEOLOGIA Y MINERIA</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -10193,13 +10193,13 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>73269.92999999999</v>
+        <v>2644.55</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>5792-23-CM25</t>
+          <t>5622-34-CM25</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -10224,12 +10224,12 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>61.702.000-9</t>
+          <t>61.979.000-6</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE GEOLOGIA Y MINERIA</t>
+          <t>SERV NACIONAL DE PESCA</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -10258,7 +10258,7 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>2644.55</v>
+        <v>2198.1</v>
       </c>
     </row>
     <row r="152">
@@ -10654,7 +10654,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>5611-131-CM25</t>
+          <t>1087-327-CM25</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -10679,12 +10679,12 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>61.813.000-2</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>SERVICIO REGIONAL DE LA VIVIENDA Y URBAN</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -10713,13 +10713,13 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>3735.76</v>
+        <v>2241.46</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>1087-327-CM25</t>
+          <t>5611-131-CM25</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -10744,12 +10744,12 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.813.000-2</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>SERVICIO REGIONAL DE LA VIVIENDA Y URBAN</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -10778,7 +10778,7 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>2241.46</v>
+        <v>3735.76</v>
       </c>
     </row>
     <row r="160">
@@ -11174,7 +11174,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>5702-916-CM25</t>
+          <t>1774-236-CM25</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -11199,12 +11199,12 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>60.804.001-3</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -11233,7 +11233,7 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>2690.66</v>
+        <v>4089.8</v>
       </c>
     </row>
     <row r="167">
@@ -11304,7 +11304,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>1774-236-CM25</t>
+          <t>5702-916-CM25</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -11329,12 +11329,12 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>60.804.001-3</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE ADUANAS</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -11363,7 +11363,7 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>4089.8</v>
+        <v>2690.66</v>
       </c>
     </row>
     <row r="169">
@@ -12799,7 +12799,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2366-56-CM26</t>
+          <t>2366-57-CM26</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -12858,13 +12858,13 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>29268.07</v>
+        <v>34561.97</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2366-57-CM26</t>
+          <t>2366-56-CM26</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -12923,7 +12923,7 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>34561.97</v>
+        <v>29268.07</v>
       </c>
     </row>
     <row r="193">
@@ -14359,7 +14359,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>1087-50-CM26</t>
+          <t>830715-31-CM26</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -14379,17 +14379,17 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>60.511.139-4</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE PARINACOTA</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -14418,7 +14418,7 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>4301.54</v>
+        <v>8540.17</v>
       </c>
     </row>
     <row r="216">
@@ -14554,7 +14554,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>830715-31-CM26</t>
+          <t>1087-50-CM26</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -14574,17 +14574,17 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>60.511.139-4</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE PARINACOTA</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -14613,13 +14613,13 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>8540.17</v>
+        <v>4301.54</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>5855-105-CM26</t>
+          <t>5855-106-CM26</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -14678,13 +14678,13 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>83211.14</v>
+        <v>77965.63</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>5855-106-CM26</t>
+          <t>5855-105-CM26</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -14743,7 +14743,7 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>77965.63</v>
+        <v>83211.14</v>
       </c>
     </row>
     <row r="221">
@@ -15789,7 +15789,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>720-103-CM26</t>
+          <t>830715-34-CM26</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -15804,22 +15804,22 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>60.511.139-4</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE PARINACOTA</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -15848,13 +15848,13 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>77431.35000000001</v>
+        <v>17078.43</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>1443565-16-CM26</t>
+          <t>720-103-CM26</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -15874,17 +15874,17 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>61.312.000-9</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>INIA</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -15913,13 +15913,13 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>3011.41</v>
+        <v>77431.35000000001</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>941739-38-CM26</t>
+          <t>1443565-16-CM26</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -15934,7 +15934,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
@@ -15944,12 +15944,12 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>70.770.800-K</t>
+          <t>61.312.000-9</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>INIA</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -15978,7 +15978,7 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>19079.69</v>
+        <v>3011.41</v>
       </c>
     </row>
     <row r="240">
@@ -16049,7 +16049,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>5702-350-CM26</t>
+          <t>941739-38-CM26</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -16064,22 +16064,22 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>70.770.800-K</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -16108,13 +16108,13 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>2754.79</v>
+        <v>19079.69</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>635-642-CM26</t>
+          <t>830715-36-CM26</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -16129,22 +16129,22 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>61.606.000-7</t>
+          <t>60.511.139-4</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE PARINACOTA</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -16173,13 +16173,13 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>8941.84</v>
+        <v>16781</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>1087-115-CM26</t>
+          <t>5702-350-CM26</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -16194,7 +16194,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
@@ -16204,12 +16204,12 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -16238,13 +16238,13 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>8794.24</v>
+        <v>2754.79</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>5702-380-CM26</t>
+          <t>635-642-CM26</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -16254,12 +16254,12 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
@@ -16269,12 +16269,12 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>61.606.000-7</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -16303,13 +16303,13 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>2799.83</v>
+        <v>8941.84</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>720-153-CM26</t>
+          <t>1087-115-CM26</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -16319,12 +16319,12 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
@@ -16334,12 +16334,12 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -16368,13 +16368,13 @@
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>62497.17</v>
+        <v>8794.24</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>1075963-7514-CM26</t>
+          <t>830715-41-CM26</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -16389,7 +16389,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -16399,12 +16399,12 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>60.511.139-4</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE PARINACOTA</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -16433,13 +16433,13 @@
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>6779.96</v>
+        <v>8802.1</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>696027-27-CM26</t>
+          <t>5702-380-CM26</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -16454,22 +16454,22 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -16498,13 +16498,13 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>4352.98</v>
+        <v>2799.83</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>5667-67-CM26</t>
+          <t>720-153-CM26</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -16519,22 +16519,22 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>61.979.080-4</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -16563,13 +16563,13 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>2347.24</v>
+        <v>62497.17</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>1087-130-CM26</t>
+          <t>1075963-7514-CM26</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -16584,22 +16584,22 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -16628,13 +16628,13 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>2816.97</v>
+        <v>6779.96</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>5702-428-CM26</t>
+          <t>696027-27-CM26</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -16649,22 +16649,22 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -16693,13 +16693,13 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>2808.58</v>
+        <v>4352.98</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>5702-427-CM26</t>
+          <t>5667-67-CM26</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -16714,22 +16714,22 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>61.979.080-4</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>2808.58</v>
+        <v>2347.24</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>1337362-33-CM26</t>
+          <t>1087-130-CM26</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -16779,7 +16779,7 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
@@ -16789,12 +16789,12 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -16823,13 +16823,13 @@
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>2425.19</v>
+        <v>2816.97</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>509920-5-CM26</t>
+          <t>5702-427-CM26</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -16844,22 +16844,22 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -16888,13 +16888,13 @@
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>2433.61</v>
+        <v>2808.58</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>4022-333-CM26</t>
+          <t>5702-428-CM26</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -16909,22 +16909,22 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>69.250.800-9</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE PUTRE</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -16953,13 +16953,13 @@
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>22638.26</v>
+        <v>2808.58</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>720-165-CM26</t>
+          <t>1337362-33-CM26</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -16974,7 +16974,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
@@ -16984,12 +16984,12 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -17018,13 +17018,13 @@
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>7321.46</v>
+        <v>2425.19</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>5667-72-CM26</t>
+          <t>720-165-CM26</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -17039,7 +17039,7 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
@@ -17049,12 +17049,12 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>61.979.080-4</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -17083,13 +17083,13 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>2387.3</v>
+        <v>7321.46</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>1087-139-CM26</t>
+          <t>509920-5-CM26</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -17104,22 +17104,22 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -17148,13 +17148,13 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>3312.06</v>
+        <v>2433.61</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>1075963-8208-CM26</t>
+          <t>4022-333-CM26</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -17169,7 +17169,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
@@ -17179,12 +17179,12 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>69.250.800-9</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PUTRE</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -17213,13 +17213,13 @@
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>4590.53</v>
+        <v>22638.26</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>1774-74-CM26</t>
+          <t>5667-72-CM26</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -17234,7 +17234,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
@@ -17244,12 +17244,12 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>60.804.001-3</t>
+          <t>61.979.080-4</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE ADUANAS</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -17278,13 +17278,13 @@
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>5044.46</v>
+        <v>2387.3</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>696027-35-CM26</t>
+          <t>1087-139-CM26</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -17299,22 +17299,22 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -17343,13 +17343,13 @@
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>6658.05</v>
+        <v>3312.06</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>2369-67-CM26</t>
+          <t>1075963-8208-CM26</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -17364,22 +17364,22 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -17389,17 +17389,17 @@
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J261" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K261" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L261" t="inlineStr">
@@ -17408,13 +17408,13 @@
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>0</v>
+        <v>4590.53</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>1075963-8659-CM26</t>
+          <t>1774-74-CM26</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -17424,27 +17424,27 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>60.804.001-3</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -17473,13 +17473,13 @@
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>5287.65</v>
+        <v>5044.46</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>1075963-8732-CM26</t>
+          <t>2369-67-CM26</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -17489,12 +17489,12 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
@@ -17504,12 +17504,12 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -17519,17 +17519,17 @@
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J263" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K263" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L263" t="inlineStr">
@@ -17538,13 +17538,13 @@
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>7594.66</v>
+        <v>0</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>720-155-CM26</t>
+          <t>696027-35-CM26</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -17554,27 +17554,27 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -17603,13 +17603,13 @@
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>7742.83</v>
+        <v>6658.05</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>2366-434-CM26</t>
+          <t>830715-43-CM26</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -17619,27 +17619,27 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>60.511.139-4</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE PARINACOTA</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -17668,13 +17668,13 @@
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>34438.48</v>
+        <v>8004.62</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>5857-25-CM26</t>
+          <t>1075963-8659-CM26</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -17689,7 +17689,7 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
@@ -17699,12 +17699,12 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>69.251.000-3</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Camarones</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -17733,13 +17733,13 @@
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>25361.43</v>
+        <v>5287.65</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>720-224-CM26</t>
+          <t>1075963-8732-CM26</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -17754,7 +17754,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
@@ -17764,12 +17764,12 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -17798,13 +17798,13 @@
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>35793.31</v>
+        <v>7594.66</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>5702-506-CM26</t>
+          <t>720-155-CM26</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -17819,7 +17819,7 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
@@ -17829,12 +17829,12 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
@@ -17863,13 +17863,13 @@
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>2703.35</v>
+        <v>7742.83</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>1075963-9267-CM26</t>
+          <t>2366-434-CM26</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -17884,22 +17884,22 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -17928,13 +17928,13 @@
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>4715.72</v>
+        <v>34438.48</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>5702-526-CM26</t>
+          <t>5857-25-CM26</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -17949,22 +17949,22 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>69.251.000-3</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>Ilustre Municipalidad de Camarones</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -17993,13 +17993,13 @@
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>4756.17</v>
+        <v>25361.43</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>4022-381-CM26</t>
+          <t>720-224-CM26</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -18014,22 +18014,22 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>69.250.800-9</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE PUTRE</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
@@ -18058,13 +18058,13 @@
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>21233</v>
+        <v>35793.31</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>1087-177-CM26</t>
+          <t>5702-506-CM26</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -18074,12 +18074,12 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
@@ -18089,12 +18089,12 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -18123,13 +18123,13 @@
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>6318.51</v>
+        <v>2703.35</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>1084148-71-CM26</t>
+          <t>1075963-9267-CM26</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -18139,27 +18139,27 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -18188,13 +18188,13 @@
         </is>
       </c>
       <c r="M273" s="2" t="n">
-        <v>3290.3</v>
+        <v>4715.72</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>1075963-10575-CM26</t>
+          <t>830715-51-CM26</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -18204,12 +18204,12 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
@@ -18219,12 +18219,12 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>60.511.139-4</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE PARINACOTA</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -18253,13 +18253,13 @@
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>4893.09</v>
+        <v>7103.34</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>1075963-10724-CM26</t>
+          <t>5702-526-CM26</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -18269,27 +18269,27 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -18318,13 +18318,13 @@
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>4886.93</v>
+        <v>4756.17</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>720-258-CM26</t>
+          <t>4022-381-CM26</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -18334,27 +18334,27 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>69.250.800-9</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PUTRE</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -18383,13 +18383,13 @@
         </is>
       </c>
       <c r="M276" s="2" t="n">
-        <v>4188.8</v>
+        <v>21233</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>5360-204-CM26</t>
+          <t>1087-177-CM26</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -18404,22 +18404,22 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -18448,13 +18448,13 @@
         </is>
       </c>
       <c r="M277" s="2" t="n">
-        <v>6279.05</v>
+        <v>6318.51</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>1232837-198-CM26</t>
+          <t>1084148-71-CM26</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -18469,22 +18469,22 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>65.166.511-6</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE FOMENTO   PRODUCTIVO DE ARICA</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
@@ -18513,13 +18513,13 @@
         </is>
       </c>
       <c r="M278" s="2" t="n">
-        <v>2336.3</v>
+        <v>3290.3</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>1075963-10879-CM26</t>
+          <t>1075963-10575-CM26</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -18534,7 +18534,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
@@ -18578,13 +18578,13 @@
         </is>
       </c>
       <c r="M279" s="2" t="n">
-        <v>4849.17</v>
+        <v>4893.09</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>1443565-42-CM26</t>
+          <t>720-258-CM26</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -18599,22 +18599,22 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>61.312.000-9</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>INIA</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -18643,13 +18643,13 @@
         </is>
       </c>
       <c r="M280" s="2" t="n">
-        <v>9533.76</v>
+        <v>4188.8</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>5702-616-CM26</t>
+          <t>1075963-10724-CM26</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -18664,22 +18664,22 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
@@ -18708,13 +18708,13 @@
         </is>
       </c>
       <c r="M281" s="2" t="n">
-        <v>4899.72</v>
+        <v>4886.93</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>5611-75-CM26</t>
+          <t>5360-204-CM26</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -18729,22 +18729,22 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>61.813.000-2</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>SERVICIO REGIONAL DE LA VIVIENDA Y URBAN</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -18773,13 +18773,13 @@
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>6532.96</v>
+        <v>6279.05</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>5649-35-CM26</t>
+          <t>830715-58-CM26</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -18794,22 +18794,22 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>61.979.030-8</t>
+          <t>60.511.139-4</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>MINISTERIO DE BIENES NACIONALES</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE PARINACOTA</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
@@ -18838,13 +18838,13 @@
         </is>
       </c>
       <c r="M283" s="2" t="n">
-        <v>2323.7</v>
+        <v>7349.91</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>5358-215-CM26</t>
+          <t>1232837-198-CM26</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -18859,7 +18859,7 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
@@ -18869,12 +18869,12 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>65.166.511-6</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>CORPORACION MUNICIPAL DE FOMENTO   PRODUCTIVO DE ARICA</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -18903,13 +18903,13 @@
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>11838.4</v>
+        <v>2336.3</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>1075963-11564-CM26</t>
+          <t>1075963-10879-CM26</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -18919,12 +18919,12 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>sep-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
@@ -18968,13 +18968,13 @@
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>5128.59</v>
+        <v>4849.17</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>1087-197-CM26</t>
+          <t>830715-63-CM26</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -18984,27 +18984,27 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>sep-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>60.511.139-4</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE PARINACOTA</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
@@ -19033,13 +19033,13 @@
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>2321.22</v>
+        <v>14501.26</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>830715-68-CM26</t>
+          <t>5611-75-CM26</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -19049,27 +19049,27 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>sep-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>60.511.139-4</t>
+          <t>61.813.000-2</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE PARINACOTA</t>
+          <t>SERVICIO REGIONAL DE LA VIVIENDA Y URBAN</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
@@ -19098,13 +19098,13 @@
         </is>
       </c>
       <c r="M287" s="2" t="n">
-        <v>15333.11</v>
+        <v>6532.96</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>830715-66-CM26</t>
+          <t>1443565-42-CM26</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -19114,12 +19114,12 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>sep-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
@@ -19129,12 +19129,12 @@
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>60.511.139-4</t>
+          <t>61.312.000-9</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE PARINACOTA</t>
+          <t>INIA</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
@@ -19163,13 +19163,13 @@
         </is>
       </c>
       <c r="M288" s="2" t="n">
-        <v>8228.129999999999</v>
+        <v>9533.76</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>635-1302-CM26</t>
+          <t>5702-616-CM26</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -19179,27 +19179,27 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>sep-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>61.606.000-7</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
@@ -19228,13 +19228,13 @@
         </is>
       </c>
       <c r="M289" s="2" t="n">
-        <v>2296.27</v>
+        <v>4899.72</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>4022-468-CM26</t>
+          <t>5649-35-CM26</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -19244,27 +19244,27 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>sep-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>69.250.800-9</t>
+          <t>61.979.030-8</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE PUTRE</t>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
@@ -19293,13 +19293,13 @@
         </is>
       </c>
       <c r="M290" s="2" t="n">
-        <v>21340.85</v>
+        <v>2323.7</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>830715-70-CM26</t>
+          <t>5358-215-CM26</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -19309,12 +19309,12 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>sep-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
@@ -19324,12 +19324,12 @@
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>60.511.139-4</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE PARINACOTA</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -19358,13 +19358,13 @@
         </is>
       </c>
       <c r="M291" s="2" t="n">
-        <v>15302.97</v>
+        <v>11838.4</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>830715-71-CM26</t>
+          <t>830715-64-CM26</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -19374,12 +19374,12 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>sep-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
@@ -19423,13 +19423,13 @@
         </is>
       </c>
       <c r="M292" s="2" t="n">
-        <v>14869.35</v>
+        <v>14408.4</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>720-289-CM26</t>
+          <t>1075963-11564-CM26</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -19444,22 +19444,22 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
@@ -19488,13 +19488,13 @@
         </is>
       </c>
       <c r="M293" s="2" t="n">
-        <v>72948.71000000001</v>
+        <v>5128.59</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>5602-272-CM26</t>
+          <t>1087-197-CM26</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -19509,7 +19509,7 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
@@ -19519,12 +19519,12 @@
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
@@ -19553,13 +19553,13 @@
         </is>
       </c>
       <c r="M294" s="2" t="n">
-        <v>3752.38</v>
+        <v>2321.22</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>5855-299-CM26</t>
+          <t>830715-68-CM26</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -19574,7 +19574,7 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
@@ -19584,12 +19584,12 @@
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>69.251.000-3</t>
+          <t>60.511.139-4</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Camarones</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE PARINACOTA</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
@@ -19618,13 +19618,13 @@
         </is>
       </c>
       <c r="M295" s="2" t="n">
-        <v>44936.58</v>
+        <v>15333.11</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>1075963-12645-CM26</t>
+          <t>830715-66-CM26</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -19639,22 +19639,22 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>60.511.139-4</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE PARINACOTA</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
@@ -19683,13 +19683,13 @@
         </is>
       </c>
       <c r="M296" s="2" t="n">
-        <v>7486.85</v>
+        <v>8228.129999999999</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>830715-74-CM26</t>
+          <t>635-1302-CM26</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -19704,7 +19704,7 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
@@ -19714,12 +19714,12 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>60.511.139-4</t>
+          <t>61.606.000-7</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE PARINACOTA</t>
+          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
@@ -19748,13 +19748,13 @@
         </is>
       </c>
       <c r="M297" s="2" t="n">
-        <v>14648.72</v>
+        <v>2296.27</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>1087-206-CM26</t>
+          <t>4022-468-CM26</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -19769,7 +19769,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
@@ -19779,12 +19779,12 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.250.800-9</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PUTRE</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -19813,13 +19813,13 @@
         </is>
       </c>
       <c r="M298" s="2" t="n">
-        <v>3091.32</v>
+        <v>21340.85</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>1110404-963-CM26</t>
+          <t>830715-70-CM26</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -19834,22 +19834,22 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>60.511.139-4</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE PARINACOTA</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
@@ -19878,13 +19878,13 @@
         </is>
       </c>
       <c r="M299" s="2" t="n">
-        <v>73882.49000000001</v>
+        <v>15302.97</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>5702-701-CM26</t>
+          <t>830715-71-CM26</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -19899,22 +19899,22 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>60.511.139-4</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE PARINACOTA</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
@@ -19943,13 +19943,13 @@
         </is>
       </c>
       <c r="M300" s="2" t="n">
-        <v>2266.97</v>
+        <v>14869.35</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>1087-209-CM26</t>
+          <t>720-289-CM26</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -19959,27 +19959,27 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>oct-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
@@ -20008,13 +20008,13 @@
         </is>
       </c>
       <c r="M301" s="2" t="n">
-        <v>8461.74</v>
+        <v>72948.71000000001</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>707409-99-CM26</t>
+          <t>5602-272-CM26</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -20024,27 +20024,27 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>oct-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
@@ -20073,13 +20073,13 @@
         </is>
       </c>
       <c r="M302" s="2" t="n">
-        <v>6098.55</v>
+        <v>3752.38</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>1075963-13004-CM26</t>
+          <t>5855-299-CM26</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -20089,12 +20089,12 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>oct-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
@@ -20104,12 +20104,12 @@
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>69.251.000-3</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>Ilustre Municipalidad de Camarones</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
@@ -20138,13 +20138,13 @@
         </is>
       </c>
       <c r="M303" s="2" t="n">
-        <v>4788.95</v>
+        <v>44936.58</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>1489-28-CM26</t>
+          <t>1075963-12645-CM26</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -20154,12 +20154,12 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>oct-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
@@ -20169,12 +20169,12 @@
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>61.979.110-k</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
@@ -20203,13 +20203,13 @@
         </is>
       </c>
       <c r="M304" s="2" t="n">
-        <v>2288.78</v>
+        <v>7486.85</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>1346279-126-CM26</t>
+          <t>830715-74-CM26</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -20219,27 +20219,27 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>oct-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>60.511.139-4</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE PARINACOTA</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
@@ -20268,13 +20268,13 @@
         </is>
       </c>
       <c r="M305" s="2" t="n">
-        <v>2205.56</v>
+        <v>14648.72</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>5702-768-CM26</t>
+          <t>1087-206-CM26</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -20284,27 +20284,27 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>oct-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
@@ -20333,71 +20333,591 @@
         </is>
       </c>
       <c r="M306" s="2" t="n">
-        <v>6909.94</v>
+        <v>3091.32</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
+          <t>1110404-963-CM26</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>62.000.660-2</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+        </is>
+      </c>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I307" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J307" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L307" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M307" s="2" t="n">
+        <v>73882.49000000001</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>5702-701-CM26</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>61.979.020-0</t>
+        </is>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+        </is>
+      </c>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I308" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J308" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L308" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M308" s="2" t="n">
+        <v>2266.97</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>1087-209-CM26</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>61.313.000-4</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>CORP NACIONAL FORESTAL</t>
+        </is>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J309" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L309" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M309" s="2" t="n">
+        <v>8461.74</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>707409-99-CM26</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>70.574.900-0</t>
+        </is>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+        </is>
+      </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J310" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L310" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M310" s="2" t="n">
+        <v>6098.55</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>1075963-13004-CM26</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>61.606.001-5</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+        </is>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I311" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J311" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L311" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M311" s="2" t="n">
+        <v>4788.95</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>1489-28-CM26</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>61.979.110-k</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
+        </is>
+      </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J312" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L312" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M312" s="2" t="n">
+        <v>2288.78</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>1346279-126-CM26</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>62.000.970-9</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+        </is>
+      </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J313" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L313" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M313" s="2" t="n">
+        <v>2205.56</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>5702-768-CM26</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>61.979.020-0</t>
+        </is>
+      </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+        </is>
+      </c>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I314" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J314" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L314" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M314" s="2" t="n">
+        <v>6909.94</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
           <t>1075963-14089-CM26</t>
         </is>
       </c>
-      <c r="B307" t="inlineStr">
+      <c r="B315" t="inlineStr">
         <is>
           <t>2239-13-LR25</t>
         </is>
       </c>
-      <c r="C307" t="inlineStr">
+      <c r="C315" t="inlineStr">
         <is>
           <t>oct-2026</t>
         </is>
       </c>
-      <c r="D307" t="inlineStr">
+      <c r="D315" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="E307" t="inlineStr">
+      <c r="E315" t="inlineStr">
         <is>
           <t>Aceptada</t>
         </is>
       </c>
-      <c r="F307" t="inlineStr">
+      <c r="F315" t="inlineStr">
         <is>
           <t>61.606.001-5</t>
         </is>
       </c>
-      <c r="G307" t="inlineStr">
+      <c r="G315" t="inlineStr">
         <is>
           <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
-      <c r="H307" t="inlineStr">
-        <is>
-          <t>Arica y Parinacota</t>
-        </is>
-      </c>
-      <c r="I307" t="inlineStr">
-        <is>
-          <t>COPEC S.A.</t>
-        </is>
-      </c>
-      <c r="J307" t="inlineStr">
-        <is>
-          <t>99.520.000-7</t>
-        </is>
-      </c>
-      <c r="K307" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="L307" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M307" s="2" t="n">
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J315" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L315" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M315" s="2" t="n">
         <v>5014.29</v>
       </c>
     </row>

--- a/docs/oc-regiones/suministro-de-combustibles/arica-y-parinacota.xlsx
+++ b/docs/oc-regiones/suministro-de-combustibles/arica-y-parinacota.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M315"/>
+  <dimension ref="A1:M316"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2529,7 +2529,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>5855-64-CM25</t>
+          <t>5611-21-CM25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2554,12 +2554,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>69.251.000-3</t>
+          <t>61.813.000-2</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Camarones</t>
+          <t>SERVICIO REGIONAL DE LA VIVIENDA Y URBAN</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>32179.17</v>
+        <v>3075.26</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>5611-21-CM25</t>
+          <t>5855-64-CM25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>61.813.000-2</t>
+          <t>69.251.000-3</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>SERVICIO REGIONAL DE LA VIVIENDA Y URBAN</t>
+          <t>Ilustre Municipalidad de Camarones</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2653,7 +2653,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>3075.26</v>
+        <v>32179.17</v>
       </c>
     </row>
     <row r="35">
@@ -4024,7 +4024,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>4022-278-CM25</t>
+          <t>1084148-70-CM25</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4044,17 +4044,17 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>69.250.800-9</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE PUTRE</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -4083,7 +4083,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>21272.52</v>
+        <v>2233.61</v>
       </c>
     </row>
     <row r="57">
@@ -4154,7 +4154,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1084148-70-CM25</t>
+          <t>3527-122-CM25</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>61.101.037-0</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4213,13 +4213,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>2233.61</v>
+        <v>4148.14</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>3527-122-CM25</t>
+          <t>4022-278-CM25</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4239,17 +4239,17 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>61.101.037-0</t>
+          <t>69.250.800-9</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PUTRE</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4278,7 +4278,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>4148.14</v>
+        <v>21272.52</v>
       </c>
     </row>
     <row r="60">
@@ -4479,7 +4479,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>720-212-CM25</t>
+          <t>720-210-CM25</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4538,13 +4538,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>4781.13</v>
+        <v>10093.5</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>720-210-CM25</t>
+          <t>720-213-CM25</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4603,7 +4603,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>10093.5</v>
+        <v>65873.77</v>
       </c>
     </row>
     <row r="65">
@@ -4674,7 +4674,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>720-213-CM25</t>
+          <t>720-212-CM25</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>65873.77</v>
+        <v>4781.13</v>
       </c>
     </row>
     <row r="67">
@@ -4869,7 +4869,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1110404-471-CM25</t>
+          <t>838099-49-CM25</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>73.923.800-5</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4928,13 +4928,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>70341.48</v>
+        <v>6394.68</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>838099-49-CM25</t>
+          <t>2585-3560-CM25</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4959,12 +4959,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>73.923.800-5</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4993,13 +4993,13 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>6394.68</v>
+        <v>72473.03999999999</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2585-3560-CM25</t>
+          <t>5358-155-CM25</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5024,12 +5024,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -5058,13 +5058,13 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>72473.03999999999</v>
+        <v>4902.59</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>5358-155-CM25</t>
+          <t>1110404-471-CM25</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5089,12 +5089,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -5123,7 +5123,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>4902.59</v>
+        <v>70341.48</v>
       </c>
     </row>
     <row r="73">
@@ -6299,7 +6299,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>1346279-122-CM25</t>
+          <t>5702-509-CM25</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -6324,12 +6324,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -6364,7 +6364,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>5702-509-CM25</t>
+          <t>1346279-122-CM25</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6389,12 +6389,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6819,7 +6819,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>1572-266-CM25</t>
+          <t>1075963-23029-CM25</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6839,17 +6839,17 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6878,13 +6878,13 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>2505.69</v>
+        <v>6880.21</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>1075963-23029-CM25</t>
+          <t>963423-2609-CM25</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6904,17 +6904,17 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>61.980.850-9</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6943,13 +6943,13 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>6880.21</v>
+        <v>2192.48</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>963423-2609-CM25</t>
+          <t>1572-266-CM25</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6974,12 +6974,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>61.980.850-9</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -7008,13 +7008,13 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>2192.48</v>
+        <v>2505.69</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>720-352-CM25</t>
+          <t>5952-239-CM25</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -7034,17 +7034,17 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -7073,13 +7073,13 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>70121.09</v>
+        <v>4124.77</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>5952-239-CM25</t>
+          <t>720-352-CM25</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -7099,17 +7099,17 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -7138,7 +7138,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>4124.77</v>
+        <v>70121.09</v>
       </c>
     </row>
     <row r="104">
@@ -8184,7 +8184,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>1075963-24769-CM25</t>
+          <t>3527-258-CM25</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -8204,17 +8204,17 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>61.101.037-0</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -8243,13 +8243,13 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>4282.8</v>
+        <v>2977.02</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>3527-258-CM25</t>
+          <t>1075963-24769-CM25</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -8269,17 +8269,17 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>61.101.037-0</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -8308,7 +8308,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>2977.02</v>
+        <v>4282.8</v>
       </c>
     </row>
     <row r="122">
@@ -9939,7 +9939,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>1075963-49124-CM25</t>
+          <t>720-489-CM25</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -9959,17 +9959,17 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -9998,13 +9998,13 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>4425.39</v>
+        <v>2206.39</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>720-489-CM25</t>
+          <t>1075963-49124-CM25</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -10024,17 +10024,17 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -10063,7 +10063,7 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>2206.39</v>
+        <v>4425.39</v>
       </c>
     </row>
     <row r="149">
@@ -10654,7 +10654,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>1087-327-CM25</t>
+          <t>5611-131-CM25</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -10679,12 +10679,12 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.813.000-2</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>SERVICIO REGIONAL DE LA VIVIENDA Y URBAN</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -10713,13 +10713,13 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>2241.46</v>
+        <v>3735.76</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>5611-131-CM25</t>
+          <t>1087-327-CM25</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -10744,12 +10744,12 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>61.813.000-2</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>SERVICIO REGIONAL DE LA VIVIENDA Y URBAN</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -10778,7 +10778,7 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>3735.76</v>
+        <v>2241.46</v>
       </c>
     </row>
     <row r="160">
@@ -11434,7 +11434,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>548849-100-CM25</t>
+          <t>3527-344-CM25</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -11459,12 +11459,12 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>61.979.440-0</t>
+          <t>61.101.037-0</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>INSTITUTO DE PREVISION SOCIAL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -11493,13 +11493,13 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>3890.34</v>
+        <v>2377.43</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>3527-344-CM25</t>
+          <t>548849-100-CM25</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -11524,12 +11524,12 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>61.101.037-0</t>
+          <t>61.979.440-0</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>INSTITUTO DE PREVISION SOCIAL</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -11558,7 +11558,7 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>2377.43</v>
+        <v>3890.34</v>
       </c>
     </row>
     <row r="172">
@@ -14359,7 +14359,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>830715-31-CM26</t>
+          <t>720-97-CM26</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -14379,17 +14379,17 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>60.511.139-4</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE PARINACOTA</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -14418,13 +14418,13 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>8540.17</v>
+        <v>73348.14999999999</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>720-97-CM26</t>
+          <t>720-98-CM26</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -14483,13 +14483,13 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>73348.14999999999</v>
+        <v>18394.45</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>720-98-CM26</t>
+          <t>830715-31-CM26</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -14509,17 +14509,17 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>60.511.139-4</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE PARINACOTA</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -14548,7 +14548,7 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>18394.45</v>
+        <v>8540.17</v>
       </c>
     </row>
     <row r="218">
@@ -14879,7 +14879,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>1075963-4970-CM26</t>
+          <t>963423-62-CM26</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -14899,17 +14899,17 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>61.980.850-9</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -14938,13 +14938,13 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>5350.82</v>
+        <v>3117.95</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>963423-62-CM26</t>
+          <t>1075963-4970-CM26</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -14964,17 +14964,17 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>61.980.850-9</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -15003,7 +15003,7 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>3117.95</v>
+        <v>5350.82</v>
       </c>
     </row>
     <row r="225">
@@ -15854,7 +15854,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>720-103-CM26</t>
+          <t>1443565-16-CM26</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -15874,17 +15874,17 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.312.000-9</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>INIA</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -15913,13 +15913,13 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>77431.35000000001</v>
+        <v>3011.41</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>1443565-16-CM26</t>
+          <t>720-103-CM26</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -15939,17 +15939,17 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>61.312.000-9</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>INIA</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -15978,7 +15978,7 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>3011.41</v>
+        <v>77431.35000000001</v>
       </c>
     </row>
     <row r="240">
@@ -16504,7 +16504,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>720-153-CM26</t>
+          <t>1075963-7514-CM26</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -16524,17 +16524,17 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -16563,13 +16563,13 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>62497.17</v>
+        <v>6779.96</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>1075963-7514-CM26</t>
+          <t>720-153-CM26</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -16589,17 +16589,17 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -16628,7 +16628,7 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>6779.96</v>
+        <v>62497.17</v>
       </c>
     </row>
     <row r="250">
@@ -16829,7 +16829,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>5702-427-CM26</t>
+          <t>5702-428-CM26</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -16894,7 +16894,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>5702-428-CM26</t>
+          <t>5702-427-CM26</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -17024,7 +17024,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>720-165-CM26</t>
+          <t>509920-5-CM26</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -17044,17 +17044,17 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -17083,13 +17083,13 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>7321.46</v>
+        <v>2433.61</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>509920-5-CM26</t>
+          <t>4022-333-CM26</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>69.250.800-9</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PUTRE</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -17148,13 +17148,13 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>2433.61</v>
+        <v>22638.26</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>4022-333-CM26</t>
+          <t>720-165-CM26</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -17174,17 +17174,17 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>69.250.800-9</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE PUTRE</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -17213,7 +17213,7 @@
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>22638.26</v>
+        <v>7321.46</v>
       </c>
     </row>
     <row r="259">
@@ -17414,7 +17414,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>1774-74-CM26</t>
+          <t>2369-67-CM26</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -17439,12 +17439,12 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>60.804.001-3</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE ADUANAS</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -17454,17 +17454,17 @@
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J262" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K262" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L262" t="inlineStr">
@@ -17473,13 +17473,13 @@
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>5044.46</v>
+        <v>0</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>2369-67-CM26</t>
+          <t>696027-35-CM26</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -17499,17 +17499,17 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -17519,17 +17519,17 @@
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J263" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K263" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L263" t="inlineStr">
@@ -17538,13 +17538,13 @@
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>0</v>
+        <v>6658.05</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>696027-35-CM26</t>
+          <t>1774-74-CM26</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -17564,17 +17564,17 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>60.804.001-3</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -17603,7 +17603,7 @@
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>6658.05</v>
+        <v>5044.46</v>
       </c>
     </row>
     <row r="265">
@@ -18064,7 +18064,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>5702-506-CM26</t>
+          <t>1075963-9267-CM26</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -18084,17 +18084,17 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -18123,13 +18123,13 @@
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>2703.35</v>
+        <v>4715.72</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>1075963-9267-CM26</t>
+          <t>5702-506-CM26</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -18149,17 +18149,17 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -18188,7 +18188,7 @@
         </is>
       </c>
       <c r="M273" s="2" t="n">
-        <v>4715.72</v>
+        <v>2703.35</v>
       </c>
     </row>
     <row r="274">
@@ -18584,7 +18584,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>720-258-CM26</t>
+          <t>1075963-10724-CM26</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -18604,17 +18604,17 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -18643,13 +18643,13 @@
         </is>
       </c>
       <c r="M280" s="2" t="n">
-        <v>4188.8</v>
+        <v>4886.93</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>1075963-10724-CM26</t>
+          <t>720-258-CM26</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -18669,17 +18669,17 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
@@ -18708,13 +18708,13 @@
         </is>
       </c>
       <c r="M281" s="2" t="n">
-        <v>4886.93</v>
+        <v>4188.8</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>5360-204-CM26</t>
+          <t>830715-58-CM26</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -18739,12 +18739,12 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>60.511.139-4</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE PARINACOTA</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -18773,13 +18773,13 @@
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>6279.05</v>
+        <v>7349.91</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>830715-58-CM26</t>
+          <t>5360-204-CM26</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -18804,12 +18804,12 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>60.511.139-4</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE PARINACOTA</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
@@ -18838,7 +18838,7 @@
         </is>
       </c>
       <c r="M283" s="2" t="n">
-        <v>7349.91</v>
+        <v>6279.05</v>
       </c>
     </row>
     <row r="284">
@@ -19039,7 +19039,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>5611-75-CM26</t>
+          <t>1443565-42-CM26</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -19059,17 +19059,17 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>61.813.000-2</t>
+          <t>61.312.000-9</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>SERVICIO REGIONAL DE LA VIVIENDA Y URBAN</t>
+          <t>INIA</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
@@ -19098,13 +19098,13 @@
         </is>
       </c>
       <c r="M287" s="2" t="n">
-        <v>6532.96</v>
+        <v>9533.76</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>1443565-42-CM26</t>
+          <t>5702-616-CM26</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -19124,17 +19124,17 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>61.312.000-9</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>INIA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
@@ -19163,13 +19163,13 @@
         </is>
       </c>
       <c r="M288" s="2" t="n">
-        <v>9533.76</v>
+        <v>4899.72</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>5702-616-CM26</t>
+          <t>5611-75-CM26</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -19194,12 +19194,12 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>61.813.000-2</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO REGIONAL DE LA VIVIENDA Y URBAN</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
@@ -19228,7 +19228,7 @@
         </is>
       </c>
       <c r="M289" s="2" t="n">
-        <v>4899.72</v>
+        <v>6532.96</v>
       </c>
     </row>
     <row r="290">
@@ -19299,7 +19299,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>5358-215-CM26</t>
+          <t>830715-64-CM26</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -19324,12 +19324,12 @@
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>60.511.139-4</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE PARINACOTA</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -19358,13 +19358,13 @@
         </is>
       </c>
       <c r="M291" s="2" t="n">
-        <v>11838.4</v>
+        <v>14408.4</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>830715-64-CM26</t>
+          <t>5358-215-CM26</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -19389,12 +19389,12 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>60.511.139-4</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE PARINACOTA</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
@@ -19423,7 +19423,7 @@
         </is>
       </c>
       <c r="M292" s="2" t="n">
-        <v>14408.4</v>
+        <v>11838.4</v>
       </c>
     </row>
     <row r="293">
@@ -19709,7 +19709,7 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
@@ -20859,65 +20859,130 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
+          <t>1087-231-CM26</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>61.313.000-4</t>
+        </is>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>CORP NACIONAL FORESTAL</t>
+        </is>
+      </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J315" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L315" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M315" s="2" t="n">
+        <v>5065.93</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
           <t>1075963-14089-CM26</t>
         </is>
       </c>
-      <c r="B315" t="inlineStr">
+      <c r="B316" t="inlineStr">
         <is>
           <t>2239-13-LR25</t>
         </is>
       </c>
-      <c r="C315" t="inlineStr">
+      <c r="C316" t="inlineStr">
         <is>
           <t>oct-2026</t>
         </is>
       </c>
-      <c r="D315" t="inlineStr">
+      <c r="D316" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="E315" t="inlineStr">
+      <c r="E316" t="inlineStr">
         <is>
           <t>Aceptada</t>
         </is>
       </c>
-      <c r="F315" t="inlineStr">
+      <c r="F316" t="inlineStr">
         <is>
           <t>61.606.001-5</t>
         </is>
       </c>
-      <c r="G315" t="inlineStr">
+      <c r="G316" t="inlineStr">
         <is>
           <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
-      <c r="H315" t="inlineStr">
-        <is>
-          <t>Arica y Parinacota</t>
-        </is>
-      </c>
-      <c r="I315" t="inlineStr">
-        <is>
-          <t>COPEC S.A.</t>
-        </is>
-      </c>
-      <c r="J315" t="inlineStr">
-        <is>
-          <t>99.520.000-7</t>
-        </is>
-      </c>
-      <c r="K315" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="L315" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M315" s="2" t="n">
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I316" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J316" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L316" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M316" s="2" t="n">
         <v>5014.29</v>
       </c>
     </row>
